--- a/output/2024_A03_SECCION_A5_TABLAS.xlsx
+++ b/output/2024_A03_SECCION_A5_TABLAS.xlsx
@@ -1081,16 +1081,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1106,7 +1098,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1114,30 +1106,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1436,21 +1410,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -1464,7 +1438,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
@@ -1478,7 +1452,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
@@ -1492,7 +1466,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
@@ -1506,7 +1480,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
@@ -1520,7 +1494,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7">
@@ -1534,7 +1508,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
@@ -1558,21 +1532,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -1586,7 +1560,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3">
@@ -1600,7 +1574,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4">
@@ -1614,7 +1588,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5">
@@ -1628,7 +1602,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6">
@@ -1642,7 +1616,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7">
@@ -1656,7 +1630,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8">
@@ -1670,7 +1644,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9">
@@ -1684,7 +1658,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
@@ -1698,7 +1672,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
@@ -1712,7 +1686,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12">
@@ -1726,7 +1700,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
@@ -1740,7 +1714,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14">
@@ -1754,7 +1728,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
       <c r="B15">
@@ -1768,7 +1742,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16">
@@ -1782,7 +1756,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>26</v>
       </c>
       <c r="B17">
@@ -1796,7 +1770,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>27</v>
       </c>
       <c r="B18">
@@ -1810,7 +1784,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19">
@@ -1824,7 +1798,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>29</v>
       </c>
       <c r="B20">
@@ -1838,7 +1812,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>30</v>
       </c>
       <c r="B21">
@@ -1852,7 +1826,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>31</v>
       </c>
       <c r="B22">
@@ -1866,7 +1840,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>32</v>
       </c>
       <c r="B23">
@@ -1880,7 +1854,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24">
@@ -1894,7 +1868,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>34</v>
       </c>
       <c r="B25">
@@ -1908,7 +1882,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>35</v>
       </c>
       <c r="B26">
@@ -1922,7 +1896,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>36</v>
       </c>
       <c r="B27">
@@ -1936,7 +1910,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>37</v>
       </c>
       <c r="B28">
@@ -1950,7 +1924,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>38</v>
       </c>
       <c r="B29">
@@ -1964,7 +1938,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>39</v>
       </c>
       <c r="B30">
@@ -1978,7 +1952,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>40</v>
       </c>
       <c r="B31">
@@ -1992,7 +1966,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>41</v>
       </c>
       <c r="B32">
@@ -2006,7 +1980,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>42</v>
       </c>
       <c r="B33">
@@ -2020,7 +1994,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>43</v>
       </c>
       <c r="B34">
@@ -2034,7 +2008,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>44</v>
       </c>
       <c r="B35">
@@ -2048,7 +2022,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>45</v>
       </c>
       <c r="B36">
@@ -2062,7 +2036,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>46</v>
       </c>
       <c r="B37">
@@ -2076,7 +2050,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>47</v>
       </c>
       <c r="B38">
@@ -2090,7 +2064,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>48</v>
       </c>
       <c r="B39">
@@ -2104,7 +2078,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40">
@@ -2118,7 +2092,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>50</v>
       </c>
       <c r="B41">
@@ -2132,7 +2106,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>51</v>
       </c>
       <c r="B42">
@@ -2146,7 +2120,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>52</v>
       </c>
       <c r="B43">
@@ -2160,7 +2134,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>53</v>
       </c>
       <c r="B44">
@@ -2174,7 +2148,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>54</v>
       </c>
       <c r="B45">
@@ -2188,7 +2162,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>55</v>
       </c>
       <c r="B46">
@@ -2202,7 +2176,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>56</v>
       </c>
       <c r="B47">
@@ -2216,7 +2190,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>57</v>
       </c>
       <c r="B48">
@@ -2230,7 +2204,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>58</v>
       </c>
       <c r="B49">
@@ -2244,7 +2218,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>59</v>
       </c>
       <c r="B50">
@@ -2258,7 +2232,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>60</v>
       </c>
       <c r="B51">
@@ -2272,7 +2246,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>61</v>
       </c>
       <c r="B52">
@@ -2286,7 +2260,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>62</v>
       </c>
       <c r="B53">
@@ -2300,7 +2274,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>63</v>
       </c>
       <c r="B54">
@@ -2324,21 +2298,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -2352,7 +2326,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>65</v>
       </c>
       <c r="B3">
@@ -2366,7 +2340,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>66</v>
       </c>
       <c r="B4">
@@ -2374,7 +2348,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>67</v>
       </c>
       <c r="B5">
@@ -2385,7 +2359,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>68</v>
       </c>
       <c r="B6">
@@ -2399,7 +2373,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>69</v>
       </c>
       <c r="B7">
@@ -2413,7 +2387,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>70</v>
       </c>
       <c r="B8">
@@ -2427,7 +2401,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>71</v>
       </c>
       <c r="B9">
@@ -2441,7 +2415,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>72</v>
       </c>
       <c r="B10">
@@ -2455,7 +2429,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>73</v>
       </c>
       <c r="B11">
@@ -2469,7 +2443,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>74</v>
       </c>
       <c r="B12">
@@ -2483,7 +2457,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>75</v>
       </c>
       <c r="B13">
@@ -2497,7 +2471,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>76</v>
       </c>
       <c r="B14">
@@ -2511,7 +2485,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>77</v>
       </c>
       <c r="B15">
@@ -2525,7 +2499,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>78</v>
       </c>
       <c r="B16">
@@ -2539,7 +2513,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>79</v>
       </c>
       <c r="B17">
@@ -2553,7 +2527,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>80</v>
       </c>
       <c r="B18">
@@ -2567,7 +2541,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>81</v>
       </c>
       <c r="B19">
@@ -2581,7 +2555,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20">
@@ -2595,7 +2569,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>83</v>
       </c>
       <c r="B21">
@@ -2609,7 +2583,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>84</v>
       </c>
       <c r="B22">
@@ -2623,7 +2597,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>85</v>
       </c>
       <c r="B23">
@@ -2637,7 +2611,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>86</v>
       </c>
       <c r="B24">
@@ -2651,7 +2625,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>87</v>
       </c>
       <c r="B25">
@@ -2665,7 +2639,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>88</v>
       </c>
       <c r="B26">
@@ -2679,7 +2653,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>89</v>
       </c>
       <c r="B27">
@@ -2693,7 +2667,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>90</v>
       </c>
       <c r="B28">
@@ -2707,7 +2681,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>91</v>
       </c>
       <c r="B29">
@@ -2721,7 +2695,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>92</v>
       </c>
       <c r="B30">
@@ -2735,7 +2709,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>93</v>
       </c>
       <c r="B31">
@@ -2749,7 +2723,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>94</v>
       </c>
       <c r="B32">
@@ -2763,7 +2737,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>95</v>
       </c>
       <c r="B33">
@@ -2777,7 +2751,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>96</v>
       </c>
       <c r="B34">
@@ -2791,7 +2765,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>97</v>
       </c>
       <c r="B35">
@@ -2805,7 +2779,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>98</v>
       </c>
       <c r="B36">
@@ -2819,7 +2793,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>99</v>
       </c>
       <c r="B37">
@@ -2833,7 +2807,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>100</v>
       </c>
       <c r="B38">
@@ -2844,7 +2818,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>101</v>
       </c>
       <c r="B39">
@@ -2858,7 +2832,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>102</v>
       </c>
       <c r="B40">
@@ -2872,7 +2846,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>103</v>
       </c>
       <c r="B41">
@@ -2886,7 +2860,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>104</v>
       </c>
       <c r="B42">
@@ -2900,7 +2874,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>105</v>
       </c>
       <c r="B43">
@@ -2914,7 +2888,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>106</v>
       </c>
       <c r="B44">
@@ -2928,7 +2902,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>107</v>
       </c>
       <c r="B45">
@@ -2942,7 +2916,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>108</v>
       </c>
       <c r="B46">
@@ -2956,7 +2930,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>109</v>
       </c>
       <c r="B47">
@@ -2970,7 +2944,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>110</v>
       </c>
       <c r="B48">
@@ -2984,7 +2958,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>111</v>
       </c>
       <c r="B49">
@@ -2998,7 +2972,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>112</v>
       </c>
       <c r="B50">
@@ -3012,7 +2986,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>113</v>
       </c>
       <c r="B51">
@@ -3026,7 +3000,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>114</v>
       </c>
       <c r="B52">
@@ -3040,7 +3014,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>115</v>
       </c>
       <c r="B53">
@@ -3054,7 +3028,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>116</v>
       </c>
       <c r="B54">
@@ -3068,7 +3042,7 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>117</v>
       </c>
       <c r="B55">
@@ -3082,7 +3056,7 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>118</v>
       </c>
       <c r="B56">
@@ -3096,7 +3070,7 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>119</v>
       </c>
       <c r="B57">
@@ -3110,7 +3084,7 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>120</v>
       </c>
       <c r="B58">
@@ -3124,7 +3098,7 @@
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>121</v>
       </c>
       <c r="B59">
@@ -3138,7 +3112,7 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>122</v>
       </c>
       <c r="B60">
@@ -3152,7 +3126,7 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>123</v>
       </c>
       <c r="B61">
@@ -3166,7 +3140,7 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>124</v>
       </c>
       <c r="B62">
@@ -3180,7 +3154,7 @@
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>125</v>
       </c>
       <c r="B63">
@@ -3194,7 +3168,7 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>126</v>
       </c>
       <c r="B64">
@@ -3208,7 +3182,7 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>127</v>
       </c>
       <c r="B65">
@@ -3222,7 +3196,7 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>128</v>
       </c>
       <c r="B66">
@@ -3236,7 +3210,7 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>129</v>
       </c>
       <c r="B67">
@@ -3247,7 +3221,7 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>130</v>
       </c>
       <c r="B68">
@@ -3261,7 +3235,7 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>131</v>
       </c>
       <c r="B69">
@@ -3275,7 +3249,7 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>132</v>
       </c>
       <c r="B70">
@@ -3289,7 +3263,7 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>133</v>
       </c>
       <c r="B71">
@@ -3303,7 +3277,7 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>134</v>
       </c>
       <c r="B72">
@@ -3317,7 +3291,7 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>135</v>
       </c>
       <c r="B73">
@@ -3331,7 +3305,7 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>136</v>
       </c>
       <c r="B74">
@@ -3345,7 +3319,7 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>137</v>
       </c>
       <c r="B75">
@@ -3359,7 +3333,7 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>138</v>
       </c>
       <c r="B76">
@@ -3373,7 +3347,7 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>139</v>
       </c>
       <c r="B77">
@@ -3387,7 +3361,7 @@
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>140</v>
       </c>
       <c r="B78">
@@ -3401,7 +3375,7 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>141</v>
       </c>
       <c r="B79">
@@ -3415,7 +3389,7 @@
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>142</v>
       </c>
       <c r="B80">
@@ -3429,7 +3403,7 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>143</v>
       </c>
       <c r="B81">
@@ -3443,7 +3417,7 @@
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>144</v>
       </c>
       <c r="B82">
@@ -3457,7 +3431,7 @@
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>145</v>
       </c>
       <c r="B83">
@@ -3471,7 +3445,7 @@
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>146</v>
       </c>
       <c r="B84">
@@ -3485,7 +3459,7 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>147</v>
       </c>
       <c r="B85">
@@ -3499,7 +3473,7 @@
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>148</v>
       </c>
       <c r="B86">
@@ -3513,7 +3487,7 @@
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>149</v>
       </c>
       <c r="B87">
@@ -3527,7 +3501,7 @@
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>150</v>
       </c>
       <c r="B88">
@@ -3541,7 +3515,7 @@
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>151</v>
       </c>
       <c r="B89">
@@ -3555,7 +3529,7 @@
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>152</v>
       </c>
       <c r="B90">
@@ -3569,7 +3543,7 @@
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>153</v>
       </c>
       <c r="B91">
@@ -3583,7 +3557,7 @@
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>154</v>
       </c>
       <c r="B92">
@@ -3597,7 +3571,7 @@
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>155</v>
       </c>
       <c r="B93">
@@ -3611,7 +3585,7 @@
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>156</v>
       </c>
       <c r="B94">
@@ -3625,7 +3599,7 @@
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>157</v>
       </c>
       <c r="B95">
@@ -3639,7 +3613,7 @@
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>158</v>
       </c>
       <c r="B96">
@@ -3653,7 +3627,7 @@
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>159</v>
       </c>
       <c r="B97">
@@ -3667,7 +3641,7 @@
       </c>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>160</v>
       </c>
       <c r="B98">
@@ -3681,7 +3655,7 @@
       </c>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>161</v>
       </c>
       <c r="B99">
@@ -3695,7 +3669,7 @@
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>162</v>
       </c>
       <c r="B100">
@@ -3709,7 +3683,7 @@
       </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>163</v>
       </c>
       <c r="B101">
@@ -3723,7 +3697,7 @@
       </c>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>164</v>
       </c>
       <c r="B102">
@@ -3737,7 +3711,7 @@
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>165</v>
       </c>
       <c r="B103">
@@ -3751,7 +3725,7 @@
       </c>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>166</v>
       </c>
       <c r="B104">
@@ -3765,7 +3739,7 @@
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>167</v>
       </c>
       <c r="B105">
@@ -3779,7 +3753,7 @@
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>168</v>
       </c>
       <c r="B106">
@@ -3793,7 +3767,7 @@
       </c>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>169</v>
       </c>
       <c r="B107">
@@ -3807,7 +3781,7 @@
       </c>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>170</v>
       </c>
       <c r="B108">
@@ -3821,7 +3795,7 @@
       </c>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>171</v>
       </c>
       <c r="B109">
@@ -3835,7 +3809,7 @@
       </c>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>172</v>
       </c>
       <c r="B110">
@@ -3849,7 +3823,7 @@
       </c>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>173</v>
       </c>
       <c r="B111">
@@ -3863,7 +3837,7 @@
       </c>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>174</v>
       </c>
       <c r="B112">
@@ -3877,7 +3851,7 @@
       </c>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>175</v>
       </c>
       <c r="B113">
@@ -3891,7 +3865,7 @@
       </c>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>176</v>
       </c>
       <c r="B114">
@@ -3905,7 +3879,7 @@
       </c>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>177</v>
       </c>
       <c r="B115">
@@ -3919,7 +3893,7 @@
       </c>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>178</v>
       </c>
       <c r="B116">
@@ -3933,7 +3907,7 @@
       </c>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="1" t="s">
+      <c r="A117" t="s">
         <v>179</v>
       </c>
       <c r="B117">
@@ -3947,7 +3921,7 @@
       </c>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="1" t="s">
+      <c r="A118" t="s">
         <v>180</v>
       </c>
       <c r="B118">
@@ -3961,7 +3935,7 @@
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="1" t="s">
+      <c r="A119" t="s">
         <v>181</v>
       </c>
       <c r="B119">
@@ -3975,7 +3949,7 @@
       </c>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="1" t="s">
+      <c r="A120" t="s">
         <v>182</v>
       </c>
       <c r="B120">
@@ -3989,7 +3963,7 @@
       </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="1" t="s">
+      <c r="A121" t="s">
         <v>183</v>
       </c>
       <c r="B121">
@@ -4003,7 +3977,7 @@
       </c>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="1" t="s">
+      <c r="A122" t="s">
         <v>184</v>
       </c>
       <c r="B122">
@@ -4017,7 +3991,7 @@
       </c>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="1" t="s">
+      <c r="A123" t="s">
         <v>185</v>
       </c>
       <c r="B123">
@@ -4031,7 +4005,7 @@
       </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="1" t="s">
+      <c r="A124" t="s">
         <v>186</v>
       </c>
       <c r="B124">
@@ -4045,7 +4019,7 @@
       </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="1" t="s">
+      <c r="A125" t="s">
         <v>187</v>
       </c>
       <c r="B125">
@@ -4059,7 +4033,7 @@
       </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="1" t="s">
+      <c r="A126" t="s">
         <v>188</v>
       </c>
       <c r="B126">
@@ -4073,7 +4047,7 @@
       </c>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="1" t="s">
+      <c r="A127" t="s">
         <v>189</v>
       </c>
       <c r="B127">
@@ -4087,7 +4061,7 @@
       </c>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
         <v>190</v>
       </c>
       <c r="B128">
@@ -4101,7 +4075,7 @@
       </c>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="1" t="s">
+      <c r="A129" t="s">
         <v>191</v>
       </c>
       <c r="B129">
@@ -4115,7 +4089,7 @@
       </c>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="1" t="s">
+      <c r="A130" t="s">
         <v>192</v>
       </c>
       <c r="B130">
@@ -4129,7 +4103,7 @@
       </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="1" t="s">
+      <c r="A131" t="s">
         <v>193</v>
       </c>
       <c r="B131">
@@ -4143,7 +4117,7 @@
       </c>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="1" t="s">
+      <c r="A132" t="s">
         <v>194</v>
       </c>
       <c r="B132">
@@ -4157,7 +4131,7 @@
       </c>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="1" t="s">
+      <c r="A133" t="s">
         <v>195</v>
       </c>
       <c r="B133">
@@ -4171,7 +4145,7 @@
       </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="1" t="s">
+      <c r="A134" t="s">
         <v>196</v>
       </c>
       <c r="B134">
@@ -4185,7 +4159,7 @@
       </c>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="1" t="s">
+      <c r="A135" t="s">
         <v>197</v>
       </c>
       <c r="B135">
@@ -4199,7 +4173,7 @@
       </c>
     </row>
     <row r="136" spans="1:4">
-      <c r="A136" s="1" t="s">
+      <c r="A136" t="s">
         <v>198</v>
       </c>
       <c r="B136">
@@ -4213,7 +4187,7 @@
       </c>
     </row>
     <row r="137" spans="1:4">
-      <c r="A137" s="1" t="s">
+      <c r="A137" t="s">
         <v>199</v>
       </c>
       <c r="B137">
@@ -4227,7 +4201,7 @@
       </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="1" t="s">
+      <c r="A138" t="s">
         <v>200</v>
       </c>
       <c r="B138">
@@ -4241,7 +4215,7 @@
       </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="1" t="s">
+      <c r="A139" t="s">
         <v>201</v>
       </c>
       <c r="B139">
@@ -4255,7 +4229,7 @@
       </c>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="1" t="s">
+      <c r="A140" t="s">
         <v>202</v>
       </c>
       <c r="B140">
@@ -4269,7 +4243,7 @@
       </c>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="1" t="s">
+      <c r="A141" t="s">
         <v>203</v>
       </c>
       <c r="B141">
@@ -4283,7 +4257,7 @@
       </c>
     </row>
     <row r="142" spans="1:4">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>204</v>
       </c>
       <c r="B142">
@@ -4297,7 +4271,7 @@
       </c>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="1" t="s">
+      <c r="A143" t="s">
         <v>205</v>
       </c>
       <c r="B143">
@@ -4311,7 +4285,7 @@
       </c>
     </row>
     <row r="144" spans="1:4">
-      <c r="A144" s="1" t="s">
+      <c r="A144" t="s">
         <v>206</v>
       </c>
       <c r="B144">
@@ -4325,7 +4299,7 @@
       </c>
     </row>
     <row r="145" spans="1:4">
-      <c r="A145" s="1" t="s">
+      <c r="A145" t="s">
         <v>207</v>
       </c>
       <c r="B145">
@@ -4339,7 +4313,7 @@
       </c>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="1" t="s">
+      <c r="A146" t="s">
         <v>208</v>
       </c>
       <c r="B146">
@@ -4353,7 +4327,7 @@
       </c>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="1" t="s">
+      <c r="A147" t="s">
         <v>209</v>
       </c>
       <c r="B147">
@@ -4367,7 +4341,7 @@
       </c>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="1" t="s">
+      <c r="A148" t="s">
         <v>210</v>
       </c>
       <c r="B148">
@@ -4381,7 +4355,7 @@
       </c>
     </row>
     <row r="149" spans="1:4">
-      <c r="A149" s="1" t="s">
+      <c r="A149" t="s">
         <v>211</v>
       </c>
       <c r="B149">
@@ -4395,7 +4369,7 @@
       </c>
     </row>
     <row r="150" spans="1:4">
-      <c r="A150" s="1" t="s">
+      <c r="A150" t="s">
         <v>212</v>
       </c>
       <c r="B150">
@@ -4409,7 +4383,7 @@
       </c>
     </row>
     <row r="151" spans="1:4">
-      <c r="A151" s="1" t="s">
+      <c r="A151" t="s">
         <v>213</v>
       </c>
       <c r="B151">
@@ -4423,7 +4397,7 @@
       </c>
     </row>
     <row r="152" spans="1:4">
-      <c r="A152" s="1" t="s">
+      <c r="A152" t="s">
         <v>214</v>
       </c>
       <c r="B152">
@@ -4437,7 +4411,7 @@
       </c>
     </row>
     <row r="153" spans="1:4">
-      <c r="A153" s="1" t="s">
+      <c r="A153" t="s">
         <v>215</v>
       </c>
       <c r="B153">
@@ -4451,7 +4425,7 @@
       </c>
     </row>
     <row r="154" spans="1:4">
-      <c r="A154" s="1" t="s">
+      <c r="A154" t="s">
         <v>216</v>
       </c>
       <c r="B154">
@@ -4465,7 +4439,7 @@
       </c>
     </row>
     <row r="155" spans="1:4">
-      <c r="A155" s="1" t="s">
+      <c r="A155" t="s">
         <v>217</v>
       </c>
       <c r="B155">
@@ -4479,7 +4453,7 @@
       </c>
     </row>
     <row r="156" spans="1:4">
-      <c r="A156" s="1" t="s">
+      <c r="A156" t="s">
         <v>218</v>
       </c>
       <c r="B156">
@@ -4493,7 +4467,7 @@
       </c>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="1" t="s">
+      <c r="A157" t="s">
         <v>219</v>
       </c>
       <c r="B157">
@@ -4507,7 +4481,7 @@
       </c>
     </row>
     <row r="158" spans="1:4">
-      <c r="A158" s="1" t="s">
+      <c r="A158" t="s">
         <v>220</v>
       </c>
       <c r="B158">
@@ -4521,7 +4495,7 @@
       </c>
     </row>
     <row r="159" spans="1:4">
-      <c r="A159" s="1" t="s">
+      <c r="A159" t="s">
         <v>221</v>
       </c>
       <c r="B159">
@@ -4535,7 +4509,7 @@
       </c>
     </row>
     <row r="160" spans="1:4">
-      <c r="A160" s="1" t="s">
+      <c r="A160" t="s">
         <v>222</v>
       </c>
       <c r="B160">
@@ -4549,7 +4523,7 @@
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="1" t="s">
+      <c r="A161" t="s">
         <v>223</v>
       </c>
       <c r="B161">
@@ -4563,7 +4537,7 @@
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="1" t="s">
+      <c r="A162" t="s">
         <v>224</v>
       </c>
       <c r="B162">
@@ -4577,7 +4551,7 @@
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="1" t="s">
+      <c r="A163" t="s">
         <v>225</v>
       </c>
       <c r="B163">
@@ -4591,7 +4565,7 @@
       </c>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="1" t="s">
+      <c r="A164" t="s">
         <v>226</v>
       </c>
       <c r="B164">
@@ -4605,7 +4579,7 @@
       </c>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="1" t="s">
+      <c r="A165" t="s">
         <v>227</v>
       </c>
       <c r="B165">
@@ -4619,7 +4593,7 @@
       </c>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="1" t="s">
+      <c r="A166" t="s">
         <v>228</v>
       </c>
       <c r="B166">
@@ -4633,7 +4607,7 @@
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="1" t="s">
+      <c r="A167" t="s">
         <v>229</v>
       </c>
       <c r="B167">
@@ -4647,7 +4621,7 @@
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="1" t="s">
+      <c r="A168" t="s">
         <v>230</v>
       </c>
       <c r="B168">
@@ -4661,7 +4635,7 @@
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="1" t="s">
+      <c r="A169" t="s">
         <v>231</v>
       </c>
       <c r="B169">
@@ -4675,7 +4649,7 @@
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="1" t="s">
+      <c r="A170" t="s">
         <v>232</v>
       </c>
       <c r="B170">
@@ -4689,7 +4663,7 @@
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="1" t="s">
+      <c r="A171" t="s">
         <v>233</v>
       </c>
       <c r="B171">
@@ -4703,7 +4677,7 @@
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="1" t="s">
+      <c r="A172" t="s">
         <v>234</v>
       </c>
       <c r="B172">
@@ -4717,7 +4691,7 @@
       </c>
     </row>
     <row r="173" spans="1:4">
-      <c r="A173" s="1" t="s">
+      <c r="A173" t="s">
         <v>235</v>
       </c>
       <c r="B173">
@@ -4731,7 +4705,7 @@
       </c>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="1" t="s">
+      <c r="A174" t="s">
         <v>236</v>
       </c>
       <c r="B174">
@@ -4745,7 +4719,7 @@
       </c>
     </row>
     <row r="175" spans="1:4">
-      <c r="A175" s="1" t="s">
+      <c r="A175" t="s">
         <v>237</v>
       </c>
       <c r="B175">
@@ -4759,7 +4733,7 @@
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="1" t="s">
+      <c r="A176" t="s">
         <v>238</v>
       </c>
       <c r="B176">
@@ -4773,7 +4747,7 @@
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="1" t="s">
+      <c r="A177" t="s">
         <v>239</v>
       </c>
       <c r="B177">
@@ -4787,7 +4761,7 @@
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="1" t="s">
+      <c r="A178" t="s">
         <v>240</v>
       </c>
       <c r="B178">
@@ -4801,7 +4775,7 @@
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="1" t="s">
+      <c r="A179" t="s">
         <v>241</v>
       </c>
       <c r="B179">
@@ -4815,7 +4789,7 @@
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="1" t="s">
+      <c r="A180" t="s">
         <v>242</v>
       </c>
       <c r="B180">
@@ -4829,7 +4803,7 @@
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="1" t="s">
+      <c r="A181" t="s">
         <v>243</v>
       </c>
       <c r="B181">
@@ -4843,7 +4817,7 @@
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="1" t="s">
+      <c r="A182" t="s">
         <v>244</v>
       </c>
       <c r="B182">
@@ -4857,7 +4831,7 @@
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="1" t="s">
+      <c r="A183" t="s">
         <v>245</v>
       </c>
       <c r="B183">
@@ -4871,7 +4845,7 @@
       </c>
     </row>
     <row r="184" spans="1:4">
-      <c r="A184" s="1" t="s">
+      <c r="A184" t="s">
         <v>246</v>
       </c>
       <c r="B184">
@@ -4885,7 +4859,7 @@
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="1" t="s">
+      <c r="A185" t="s">
         <v>247</v>
       </c>
       <c r="B185">
@@ -4899,7 +4873,7 @@
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="1" t="s">
+      <c r="A186" t="s">
         <v>248</v>
       </c>
       <c r="B186">
@@ -4913,7 +4887,7 @@
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="1" t="s">
+      <c r="A187" t="s">
         <v>249</v>
       </c>
       <c r="B187">
@@ -4927,7 +4901,7 @@
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="1" t="s">
+      <c r="A188" t="s">
         <v>250</v>
       </c>
       <c r="B188">
@@ -4941,7 +4915,7 @@
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="1" t="s">
+      <c r="A189" t="s">
         <v>251</v>
       </c>
       <c r="B189">
@@ -4955,7 +4929,7 @@
       </c>
     </row>
     <row r="190" spans="1:4">
-      <c r="A190" s="1" t="s">
+      <c r="A190" t="s">
         <v>252</v>
       </c>
       <c r="B190">
@@ -4969,7 +4943,7 @@
       </c>
     </row>
     <row r="191" spans="1:4">
-      <c r="A191" s="1" t="s">
+      <c r="A191" t="s">
         <v>253</v>
       </c>
       <c r="B191">
@@ -4983,7 +4957,7 @@
       </c>
     </row>
     <row r="192" spans="1:4">
-      <c r="A192" s="1" t="s">
+      <c r="A192" t="s">
         <v>254</v>
       </c>
       <c r="B192">
@@ -4997,7 +4971,7 @@
       </c>
     </row>
     <row r="193" spans="1:4">
-      <c r="A193" s="1" t="s">
+      <c r="A193" t="s">
         <v>255</v>
       </c>
       <c r="B193">
@@ -5011,7 +4985,7 @@
       </c>
     </row>
     <row r="194" spans="1:4">
-      <c r="A194" s="1" t="s">
+      <c r="A194" t="s">
         <v>256</v>
       </c>
       <c r="B194">
@@ -5025,7 +4999,7 @@
       </c>
     </row>
     <row r="195" spans="1:4">
-      <c r="A195" s="1" t="s">
+      <c r="A195" t="s">
         <v>257</v>
       </c>
       <c r="B195">
@@ -5039,7 +5013,7 @@
       </c>
     </row>
     <row r="196" spans="1:4">
-      <c r="A196" s="1" t="s">
+      <c r="A196" t="s">
         <v>258</v>
       </c>
       <c r="B196">
@@ -5053,7 +5027,7 @@
       </c>
     </row>
     <row r="197" spans="1:4">
-      <c r="A197" s="1" t="s">
+      <c r="A197" t="s">
         <v>259</v>
       </c>
       <c r="B197">
@@ -5067,7 +5041,7 @@
       </c>
     </row>
     <row r="198" spans="1:4">
-      <c r="A198" s="1" t="s">
+      <c r="A198" t="s">
         <v>260</v>
       </c>
       <c r="B198">
@@ -5081,7 +5055,7 @@
       </c>
     </row>
     <row r="199" spans="1:4">
-      <c r="A199" s="1" t="s">
+      <c r="A199" t="s">
         <v>261</v>
       </c>
       <c r="B199">
@@ -5095,7 +5069,7 @@
       </c>
     </row>
     <row r="200" spans="1:4">
-      <c r="A200" s="1" t="s">
+      <c r="A200" t="s">
         <v>262</v>
       </c>
       <c r="B200">
@@ -5109,7 +5083,7 @@
       </c>
     </row>
     <row r="201" spans="1:4">
-      <c r="A201" s="1" t="s">
+      <c r="A201" t="s">
         <v>263</v>
       </c>
       <c r="B201">
@@ -5123,7 +5097,7 @@
       </c>
     </row>
     <row r="202" spans="1:4">
-      <c r="A202" s="1" t="s">
+      <c r="A202" t="s">
         <v>264</v>
       </c>
       <c r="B202">
@@ -5137,7 +5111,7 @@
       </c>
     </row>
     <row r="203" spans="1:4">
-      <c r="A203" s="1" t="s">
+      <c r="A203" t="s">
         <v>265</v>
       </c>
       <c r="B203">
@@ -5151,7 +5125,7 @@
       </c>
     </row>
     <row r="204" spans="1:4">
-      <c r="A204" s="1" t="s">
+      <c r="A204" t="s">
         <v>266</v>
       </c>
       <c r="B204">
@@ -5165,7 +5139,7 @@
       </c>
     </row>
     <row r="205" spans="1:4">
-      <c r="A205" s="1" t="s">
+      <c r="A205" t="s">
         <v>267</v>
       </c>
       <c r="B205">
@@ -5179,7 +5153,7 @@
       </c>
     </row>
     <row r="206" spans="1:4">
-      <c r="A206" s="1" t="s">
+      <c r="A206" t="s">
         <v>268</v>
       </c>
       <c r="B206">
@@ -5193,7 +5167,7 @@
       </c>
     </row>
     <row r="207" spans="1:4">
-      <c r="A207" s="1" t="s">
+      <c r="A207" t="s">
         <v>269</v>
       </c>
       <c r="B207">
@@ -5207,7 +5181,7 @@
       </c>
     </row>
     <row r="208" spans="1:4">
-      <c r="A208" s="1" t="s">
+      <c r="A208" t="s">
         <v>270</v>
       </c>
       <c r="B208">
@@ -5221,7 +5195,7 @@
       </c>
     </row>
     <row r="209" spans="1:4">
-      <c r="A209" s="1" t="s">
+      <c r="A209" t="s">
         <v>271</v>
       </c>
       <c r="B209">
@@ -5235,7 +5209,7 @@
       </c>
     </row>
     <row r="210" spans="1:4">
-      <c r="A210" s="1" t="s">
+      <c r="A210" t="s">
         <v>272</v>
       </c>
       <c r="B210">
@@ -5249,7 +5223,7 @@
       </c>
     </row>
     <row r="211" spans="1:4">
-      <c r="A211" s="1" t="s">
+      <c r="A211" t="s">
         <v>273</v>
       </c>
       <c r="B211">
@@ -5263,7 +5237,7 @@
       </c>
     </row>
     <row r="212" spans="1:4">
-      <c r="A212" s="1" t="s">
+      <c r="A212" t="s">
         <v>274</v>
       </c>
       <c r="B212">
@@ -5277,7 +5251,7 @@
       </c>
     </row>
     <row r="213" spans="1:4">
-      <c r="A213" s="1" t="s">
+      <c r="A213" t="s">
         <v>275</v>
       </c>
       <c r="B213">
@@ -5291,7 +5265,7 @@
       </c>
     </row>
     <row r="214" spans="1:4">
-      <c r="A214" s="1" t="s">
+      <c r="A214" t="s">
         <v>276</v>
       </c>
       <c r="B214">
@@ -5305,7 +5279,7 @@
       </c>
     </row>
     <row r="215" spans="1:4">
-      <c r="A215" s="1" t="s">
+      <c r="A215" t="s">
         <v>277</v>
       </c>
       <c r="B215">
@@ -5319,7 +5293,7 @@
       </c>
     </row>
     <row r="216" spans="1:4">
-      <c r="A216" s="1" t="s">
+      <c r="A216" t="s">
         <v>278</v>
       </c>
       <c r="B216">
@@ -5333,7 +5307,7 @@
       </c>
     </row>
     <row r="217" spans="1:4">
-      <c r="A217" s="1" t="s">
+      <c r="A217" t="s">
         <v>279</v>
       </c>
       <c r="B217">
@@ -5347,7 +5321,7 @@
       </c>
     </row>
     <row r="218" spans="1:4">
-      <c r="A218" s="1" t="s">
+      <c r="A218" t="s">
         <v>280</v>
       </c>
       <c r="B218">
@@ -5361,7 +5335,7 @@
       </c>
     </row>
     <row r="219" spans="1:4">
-      <c r="A219" s="1" t="s">
+      <c r="A219" t="s">
         <v>281</v>
       </c>
       <c r="B219">
@@ -5375,7 +5349,7 @@
       </c>
     </row>
     <row r="220" spans="1:4">
-      <c r="A220" s="1" t="s">
+      <c r="A220" t="s">
         <v>282</v>
       </c>
       <c r="B220">
@@ -5389,7 +5363,7 @@
       </c>
     </row>
     <row r="221" spans="1:4">
-      <c r="A221" s="1" t="s">
+      <c r="A221" t="s">
         <v>283</v>
       </c>
       <c r="B221">
@@ -5403,7 +5377,7 @@
       </c>
     </row>
     <row r="222" spans="1:4">
-      <c r="A222" s="1" t="s">
+      <c r="A222" t="s">
         <v>284</v>
       </c>
       <c r="B222">
@@ -5417,7 +5391,7 @@
       </c>
     </row>
     <row r="223" spans="1:4">
-      <c r="A223" s="1" t="s">
+      <c r="A223" t="s">
         <v>285</v>
       </c>
       <c r="B223">
@@ -5431,7 +5405,7 @@
       </c>
     </row>
     <row r="224" spans="1:4">
-      <c r="A224" s="1" t="s">
+      <c r="A224" t="s">
         <v>286</v>
       </c>
       <c r="B224">
@@ -5445,7 +5419,7 @@
       </c>
     </row>
     <row r="225" spans="1:4">
-      <c r="A225" s="1" t="s">
+      <c r="A225" t="s">
         <v>287</v>
       </c>
       <c r="B225">
@@ -5459,7 +5433,7 @@
       </c>
     </row>
     <row r="226" spans="1:4">
-      <c r="A226" s="1" t="s">
+      <c r="A226" t="s">
         <v>288</v>
       </c>
       <c r="B226">
@@ -5473,7 +5447,7 @@
       </c>
     </row>
     <row r="227" spans="1:4">
-      <c r="A227" s="1" t="s">
+      <c r="A227" t="s">
         <v>289</v>
       </c>
       <c r="B227">
@@ -5487,7 +5461,7 @@
       </c>
     </row>
     <row r="228" spans="1:4">
-      <c r="A228" s="1" t="s">
+      <c r="A228" t="s">
         <v>290</v>
       </c>
       <c r="B228">
@@ -5501,7 +5475,7 @@
       </c>
     </row>
     <row r="229" spans="1:4">
-      <c r="A229" s="1" t="s">
+      <c r="A229" t="s">
         <v>291</v>
       </c>
       <c r="B229">
@@ -5515,7 +5489,7 @@
       </c>
     </row>
     <row r="230" spans="1:4">
-      <c r="A230" s="1" t="s">
+      <c r="A230" t="s">
         <v>292</v>
       </c>
       <c r="B230">
@@ -5529,7 +5503,7 @@
       </c>
     </row>
     <row r="231" spans="1:4">
-      <c r="A231" s="1" t="s">
+      <c r="A231" t="s">
         <v>293</v>
       </c>
       <c r="B231">
@@ -5543,7 +5517,7 @@
       </c>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="1" t="s">
+      <c r="A232" t="s">
         <v>294</v>
       </c>
       <c r="B232">
@@ -5557,7 +5531,7 @@
       </c>
     </row>
     <row r="233" spans="1:4">
-      <c r="A233" s="1" t="s">
+      <c r="A233" t="s">
         <v>295</v>
       </c>
       <c r="B233">
@@ -5571,7 +5545,7 @@
       </c>
     </row>
     <row r="234" spans="1:4">
-      <c r="A234" s="1" t="s">
+      <c r="A234" t="s">
         <v>296</v>
       </c>
       <c r="B234">
@@ -5585,7 +5559,7 @@
       </c>
     </row>
     <row r="235" spans="1:4">
-      <c r="A235" s="1" t="s">
+      <c r="A235" t="s">
         <v>297</v>
       </c>
       <c r="B235">
@@ -5599,7 +5573,7 @@
       </c>
     </row>
     <row r="236" spans="1:4">
-      <c r="A236" s="1" t="s">
+      <c r="A236" t="s">
         <v>298</v>
       </c>
       <c r="B236">
@@ -5613,7 +5587,7 @@
       </c>
     </row>
     <row r="237" spans="1:4">
-      <c r="A237" s="1" t="s">
+      <c r="A237" t="s">
         <v>299</v>
       </c>
       <c r="B237">
@@ -5627,7 +5601,7 @@
       </c>
     </row>
     <row r="238" spans="1:4">
-      <c r="A238" s="1" t="s">
+      <c r="A238" t="s">
         <v>300</v>
       </c>
       <c r="B238">
@@ -5641,7 +5615,7 @@
       </c>
     </row>
     <row r="239" spans="1:4">
-      <c r="A239" s="1" t="s">
+      <c r="A239" t="s">
         <v>301</v>
       </c>
       <c r="B239">
@@ -5655,7 +5629,7 @@
       </c>
     </row>
     <row r="240" spans="1:4">
-      <c r="A240" s="1" t="s">
+      <c r="A240" t="s">
         <v>302</v>
       </c>
       <c r="B240">
@@ -5669,7 +5643,7 @@
       </c>
     </row>
     <row r="241" spans="1:4">
-      <c r="A241" s="1" t="s">
+      <c r="A241" t="s">
         <v>303</v>
       </c>
       <c r="B241">
@@ -5683,7 +5657,7 @@
       </c>
     </row>
     <row r="242" spans="1:4">
-      <c r="A242" s="1" t="s">
+      <c r="A242" t="s">
         <v>304</v>
       </c>
       <c r="B242">
@@ -5697,7 +5671,7 @@
       </c>
     </row>
     <row r="243" spans="1:4">
-      <c r="A243" s="1" t="s">
+      <c r="A243" t="s">
         <v>305</v>
       </c>
       <c r="B243">
@@ -5711,7 +5685,7 @@
       </c>
     </row>
     <row r="244" spans="1:4">
-      <c r="A244" s="1" t="s">
+      <c r="A244" t="s">
         <v>306</v>
       </c>
       <c r="B244">
@@ -5725,7 +5699,7 @@
       </c>
     </row>
     <row r="245" spans="1:4">
-      <c r="A245" s="1" t="s">
+      <c r="A245" t="s">
         <v>307</v>
       </c>
       <c r="B245">
@@ -5739,7 +5713,7 @@
       </c>
     </row>
     <row r="246" spans="1:4">
-      <c r="A246" s="1" t="s">
+      <c r="A246" t="s">
         <v>308</v>
       </c>
       <c r="B246">
@@ -5753,7 +5727,7 @@
       </c>
     </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="1" t="s">
+      <c r="A247" t="s">
         <v>309</v>
       </c>
       <c r="B247">
@@ -5767,7 +5741,7 @@
       </c>
     </row>
     <row r="248" spans="1:4">
-      <c r="A248" s="1" t="s">
+      <c r="A248" t="s">
         <v>310</v>
       </c>
       <c r="B248">
@@ -5781,7 +5755,7 @@
       </c>
     </row>
     <row r="249" spans="1:4">
-      <c r="A249" s="1" t="s">
+      <c r="A249" t="s">
         <v>311</v>
       </c>
       <c r="B249">
@@ -5795,7 +5769,7 @@
       </c>
     </row>
     <row r="250" spans="1:4">
-      <c r="A250" s="1" t="s">
+      <c r="A250" t="s">
         <v>312</v>
       </c>
       <c r="B250">
@@ -5809,7 +5783,7 @@
       </c>
     </row>
     <row r="251" spans="1:4">
-      <c r="A251" s="1" t="s">
+      <c r="A251" t="s">
         <v>313</v>
       </c>
       <c r="B251">
@@ -5823,7 +5797,7 @@
       </c>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="1" t="s">
+      <c r="A252" t="s">
         <v>314</v>
       </c>
       <c r="B252">
@@ -5837,7 +5811,7 @@
       </c>
     </row>
     <row r="253" spans="1:4">
-      <c r="A253" s="1" t="s">
+      <c r="A253" t="s">
         <v>315</v>
       </c>
       <c r="B253">
@@ -5851,7 +5825,7 @@
       </c>
     </row>
     <row r="254" spans="1:4">
-      <c r="A254" s="1" t="s">
+      <c r="A254" t="s">
         <v>316</v>
       </c>
       <c r="C254">
@@ -5859,7 +5833,7 @@
       </c>
     </row>
     <row r="255" spans="1:4">
-      <c r="A255" s="1" t="s">
+      <c r="A255" t="s">
         <v>317</v>
       </c>
       <c r="B255">
@@ -5873,7 +5847,7 @@
       </c>
     </row>
     <row r="256" spans="1:4">
-      <c r="A256" s="1" t="s">
+      <c r="A256" t="s">
         <v>318</v>
       </c>
       <c r="B256">
@@ -5887,7 +5861,7 @@
       </c>
     </row>
     <row r="257" spans="1:4">
-      <c r="A257" s="1" t="s">
+      <c r="A257" t="s">
         <v>319</v>
       </c>
       <c r="B257">
@@ -5901,7 +5875,7 @@
       </c>
     </row>
     <row r="258" spans="1:4">
-      <c r="A258" s="1" t="s">
+      <c r="A258" t="s">
         <v>320</v>
       </c>
       <c r="B258">
@@ -5915,7 +5889,7 @@
       </c>
     </row>
     <row r="259" spans="1:4">
-      <c r="A259" s="1" t="s">
+      <c r="A259" t="s">
         <v>321</v>
       </c>
       <c r="B259">
@@ -5929,7 +5903,7 @@
       </c>
     </row>
     <row r="260" spans="1:4">
-      <c r="A260" s="1" t="s">
+      <c r="A260" t="s">
         <v>322</v>
       </c>
       <c r="B260">
@@ -5940,7 +5914,7 @@
       </c>
     </row>
     <row r="261" spans="1:4">
-      <c r="A261" s="1" t="s">
+      <c r="A261" t="s">
         <v>323</v>
       </c>
       <c r="B261">
@@ -5951,7 +5925,7 @@
       </c>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="1" t="s">
+      <c r="A262" t="s">
         <v>324</v>
       </c>
       <c r="C262">
@@ -5959,7 +5933,7 @@
       </c>
     </row>
     <row r="263" spans="1:4">
-      <c r="A263" s="1" t="s">
+      <c r="A263" t="s">
         <v>325</v>
       </c>
       <c r="B263">
@@ -5973,7 +5947,7 @@
       </c>
     </row>
     <row r="264" spans="1:4">
-      <c r="A264" s="1" t="s">
+      <c r="A264" t="s">
         <v>326</v>
       </c>
       <c r="B264">
@@ -5987,7 +5961,7 @@
       </c>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="1" t="s">
+      <c r="A265" t="s">
         <v>327</v>
       </c>
       <c r="B265">
@@ -6001,7 +5975,7 @@
       </c>
     </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="1" t="s">
+      <c r="A266" t="s">
         <v>328</v>
       </c>
       <c r="B266">
@@ -6015,7 +5989,7 @@
       </c>
     </row>
     <row r="267" spans="1:4">
-      <c r="A267" s="1" t="s">
+      <c r="A267" t="s">
         <v>329</v>
       </c>
       <c r="B267">
@@ -6029,7 +6003,7 @@
       </c>
     </row>
     <row r="268" spans="1:4">
-      <c r="A268" s="1" t="s">
+      <c r="A268" t="s">
         <v>330</v>
       </c>
       <c r="B268">
@@ -6043,7 +6017,7 @@
       </c>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="1" t="s">
+      <c r="A269" t="s">
         <v>331</v>
       </c>
       <c r="B269">
@@ -6057,7 +6031,7 @@
       </c>
     </row>
     <row r="270" spans="1:4">
-      <c r="A270" s="1" t="s">
+      <c r="A270" t="s">
         <v>332</v>
       </c>
       <c r="B270">
@@ -6068,7 +6042,7 @@
       </c>
     </row>
     <row r="271" spans="1:4">
-      <c r="A271" s="1" t="s">
+      <c r="A271" t="s">
         <v>333</v>
       </c>
       <c r="B271">
@@ -6082,7 +6056,7 @@
       </c>
     </row>
     <row r="272" spans="1:4">
-      <c r="A272" s="1" t="s">
+      <c r="A272" t="s">
         <v>334</v>
       </c>
       <c r="B272">
@@ -6096,7 +6070,7 @@
       </c>
     </row>
     <row r="273" spans="1:4">
-      <c r="A273" s="1" t="s">
+      <c r="A273" t="s">
         <v>335</v>
       </c>
       <c r="B273">
@@ -6110,7 +6084,7 @@
       </c>
     </row>
     <row r="274" spans="1:4">
-      <c r="A274" s="1" t="s">
+      <c r="A274" t="s">
         <v>336</v>
       </c>
       <c r="B274">
@@ -6124,7 +6098,7 @@
       </c>
     </row>
     <row r="275" spans="1:4">
-      <c r="A275" s="1" t="s">
+      <c r="A275" t="s">
         <v>337</v>
       </c>
       <c r="B275">
@@ -6138,7 +6112,7 @@
       </c>
     </row>
     <row r="276" spans="1:4">
-      <c r="A276" s="1" t="s">
+      <c r="A276" t="s">
         <v>338</v>
       </c>
       <c r="B276">
@@ -6152,7 +6126,7 @@
       </c>
     </row>
     <row r="277" spans="1:4">
-      <c r="A277" s="1" t="s">
+      <c r="A277" t="s">
         <v>339</v>
       </c>
       <c r="B277">
@@ -6166,7 +6140,7 @@
       </c>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" s="1" t="s">
+      <c r="A278" t="s">
         <v>340</v>
       </c>
       <c r="B278">
@@ -6180,7 +6154,7 @@
       </c>
     </row>
     <row r="279" spans="1:4">
-      <c r="A279" s="1" t="s">
+      <c r="A279" t="s">
         <v>341</v>
       </c>
       <c r="B279">
@@ -6194,7 +6168,7 @@
       </c>
     </row>
     <row r="280" spans="1:4">
-      <c r="A280" s="1" t="s">
+      <c r="A280" t="s">
         <v>342</v>
       </c>
       <c r="B280">
@@ -6208,7 +6182,7 @@
       </c>
     </row>
     <row r="281" spans="1:4">
-      <c r="A281" s="1" t="s">
+      <c r="A281" t="s">
         <v>343</v>
       </c>
       <c r="B281">
@@ -6222,7 +6196,7 @@
       </c>
     </row>
     <row r="282" spans="1:4">
-      <c r="A282" s="1" t="s">
+      <c r="A282" t="s">
         <v>344</v>
       </c>
       <c r="B282">
@@ -6236,7 +6210,7 @@
       </c>
     </row>
     <row r="283" spans="1:4">
-      <c r="A283" s="1" t="s">
+      <c r="A283" t="s">
         <v>345</v>
       </c>
       <c r="B283">
@@ -6250,7 +6224,7 @@
       </c>
     </row>
     <row r="284" spans="1:4">
-      <c r="A284" s="1" t="s">
+      <c r="A284" t="s">
         <v>346</v>
       </c>
       <c r="C284">
@@ -6258,7 +6232,7 @@
       </c>
     </row>
     <row r="285" spans="1:4">
-      <c r="A285" s="1" t="s">
+      <c r="A285" t="s">
         <v>347</v>
       </c>
       <c r="B285">
@@ -6272,7 +6246,7 @@
       </c>
     </row>
     <row r="286" spans="1:4">
-      <c r="A286" s="1" t="s">
+      <c r="A286" t="s">
         <v>348</v>
       </c>
       <c r="B286">
@@ -6286,7 +6260,7 @@
       </c>
     </row>
     <row r="287" spans="1:4">
-      <c r="A287" s="1" t="s">
+      <c r="A287" t="s">
         <v>349</v>
       </c>
       <c r="B287">
@@ -6310,21 +6284,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -6338,7 +6312,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
@@ -6352,7 +6326,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
@@ -6366,7 +6340,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
@@ -6380,7 +6354,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
@@ -6394,7 +6368,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7">
@@ -6408,7 +6382,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
@@ -6432,21 +6406,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -6460,7 +6434,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3">
@@ -6474,7 +6448,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4">
@@ -6488,7 +6462,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5">
@@ -6502,7 +6476,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6">
@@ -6516,7 +6490,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7">
@@ -6530,7 +6504,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8">
@@ -6544,7 +6518,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9">
@@ -6558,7 +6532,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
@@ -6572,7 +6546,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
@@ -6586,7 +6560,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12">
@@ -6600,7 +6574,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
@@ -6614,7 +6588,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14">
@@ -6628,7 +6602,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
       <c r="B15">
@@ -6642,7 +6616,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16">
@@ -6656,7 +6630,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>26</v>
       </c>
       <c r="B17">
@@ -6670,7 +6644,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>27</v>
       </c>
       <c r="B18">
@@ -6684,7 +6658,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19">
@@ -6698,7 +6672,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>29</v>
       </c>
       <c r="B20">
@@ -6712,7 +6686,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>30</v>
       </c>
       <c r="B21">
@@ -6726,7 +6700,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>31</v>
       </c>
       <c r="B22">
@@ -6740,7 +6714,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>32</v>
       </c>
       <c r="B23">
@@ -6754,7 +6728,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24">
@@ -6768,7 +6742,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>34</v>
       </c>
       <c r="B25">
@@ -6782,7 +6756,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>35</v>
       </c>
       <c r="B26">
@@ -6796,7 +6770,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>36</v>
       </c>
       <c r="B27">
@@ -6810,7 +6784,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>37</v>
       </c>
       <c r="B28">
@@ -6824,7 +6798,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>38</v>
       </c>
       <c r="B29">
@@ -6838,7 +6812,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>39</v>
       </c>
       <c r="B30">
@@ -6852,7 +6826,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>40</v>
       </c>
       <c r="B31">
@@ -6866,7 +6840,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>41</v>
       </c>
       <c r="B32">
@@ -6880,7 +6854,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>42</v>
       </c>
       <c r="B33">
@@ -6894,7 +6868,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>43</v>
       </c>
       <c r="B34">
@@ -6908,7 +6882,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>44</v>
       </c>
       <c r="B35">
@@ -6922,7 +6896,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>45</v>
       </c>
       <c r="B36">
@@ -6936,7 +6910,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>46</v>
       </c>
       <c r="B37">
@@ -6950,7 +6924,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>47</v>
       </c>
       <c r="B38">
@@ -6964,7 +6938,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>48</v>
       </c>
       <c r="B39">
@@ -6978,7 +6952,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40">
@@ -6992,7 +6966,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>50</v>
       </c>
       <c r="B41">
@@ -7006,7 +6980,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>51</v>
       </c>
       <c r="B42">
@@ -7020,7 +6994,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>52</v>
       </c>
       <c r="B43">
@@ -7034,7 +7008,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>53</v>
       </c>
       <c r="B44">
@@ -7048,7 +7022,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>54</v>
       </c>
       <c r="B45">
@@ -7062,7 +7036,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>55</v>
       </c>
       <c r="B46">
@@ -7076,7 +7050,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>56</v>
       </c>
       <c r="B47">
@@ -7090,7 +7064,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>57</v>
       </c>
       <c r="B48">
@@ -7104,7 +7078,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>58</v>
       </c>
       <c r="B49">
@@ -7118,7 +7092,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>59</v>
       </c>
       <c r="B50">
@@ -7132,7 +7106,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>60</v>
       </c>
       <c r="B51">
@@ -7146,7 +7120,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>61</v>
       </c>
       <c r="B52">
@@ -7160,7 +7134,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>62</v>
       </c>
       <c r="B53">
@@ -7174,7 +7148,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>63</v>
       </c>
       <c r="B54">
@@ -7198,21 +7172,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -7226,7 +7200,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>65</v>
       </c>
       <c r="B3">
@@ -7240,7 +7214,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>66</v>
       </c>
       <c r="B4">
@@ -7248,7 +7222,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>67</v>
       </c>
       <c r="B5">
@@ -7262,7 +7236,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>68</v>
       </c>
       <c r="B6">
@@ -7276,7 +7250,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>69</v>
       </c>
       <c r="B7">
@@ -7290,7 +7264,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>70</v>
       </c>
       <c r="B8">
@@ -7304,7 +7278,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>71</v>
       </c>
       <c r="B9">
@@ -7318,7 +7292,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>72</v>
       </c>
       <c r="B10">
@@ -7332,7 +7306,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>73</v>
       </c>
       <c r="B11">
@@ -7346,7 +7320,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>74</v>
       </c>
       <c r="B12">
@@ -7360,7 +7334,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>75</v>
       </c>
       <c r="B13">
@@ -7374,7 +7348,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>76</v>
       </c>
       <c r="B14">
@@ -7388,7 +7362,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>77</v>
       </c>
       <c r="B15">
@@ -7402,7 +7376,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>78</v>
       </c>
       <c r="B16">
@@ -7416,7 +7390,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>79</v>
       </c>
       <c r="B17">
@@ -7430,7 +7404,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>80</v>
       </c>
       <c r="B18">
@@ -7444,7 +7418,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>81</v>
       </c>
       <c r="B19">
@@ -7458,7 +7432,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20">
@@ -7472,7 +7446,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>83</v>
       </c>
       <c r="B21">
@@ -7486,7 +7460,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>84</v>
       </c>
       <c r="B22">
@@ -7500,7 +7474,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>85</v>
       </c>
       <c r="B23">
@@ -7514,7 +7488,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>86</v>
       </c>
       <c r="B24">
@@ -7528,7 +7502,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>87</v>
       </c>
       <c r="B25">
@@ -7542,7 +7516,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>88</v>
       </c>
       <c r="B26">
@@ -7556,7 +7530,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>89</v>
       </c>
       <c r="B27">
@@ -7570,7 +7544,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>90</v>
       </c>
       <c r="B28">
@@ -7584,7 +7558,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>91</v>
       </c>
       <c r="B29">
@@ -7598,7 +7572,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>92</v>
       </c>
       <c r="B30">
@@ -7612,7 +7586,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>93</v>
       </c>
       <c r="B31">
@@ -7626,7 +7600,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>94</v>
       </c>
       <c r="B32">
@@ -7637,7 +7611,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>95</v>
       </c>
       <c r="B33">
@@ -7651,7 +7625,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>96</v>
       </c>
       <c r="B34">
@@ -7665,7 +7639,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>97</v>
       </c>
       <c r="B35">
@@ -7679,7 +7653,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>98</v>
       </c>
       <c r="B36">
@@ -7693,7 +7667,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>99</v>
       </c>
       <c r="B37">
@@ -7707,7 +7681,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>100</v>
       </c>
       <c r="B38">
@@ -7721,7 +7695,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>101</v>
       </c>
       <c r="B39">
@@ -7735,7 +7709,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>102</v>
       </c>
       <c r="B40">
@@ -7749,7 +7723,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>103</v>
       </c>
       <c r="B41">
@@ -7763,7 +7737,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>104</v>
       </c>
       <c r="B42">
@@ -7777,7 +7751,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>105</v>
       </c>
       <c r="B43">
@@ -7791,7 +7765,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>106</v>
       </c>
       <c r="B44">
@@ -7805,7 +7779,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>107</v>
       </c>
       <c r="B45">
@@ -7819,7 +7793,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>108</v>
       </c>
       <c r="B46">
@@ -7833,7 +7807,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>109</v>
       </c>
       <c r="B47">
@@ -7847,7 +7821,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>110</v>
       </c>
       <c r="B48">
@@ -7861,7 +7835,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>111</v>
       </c>
       <c r="B49">
@@ -7875,7 +7849,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>112</v>
       </c>
       <c r="B50">
@@ -7889,7 +7863,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>113</v>
       </c>
       <c r="B51">
@@ -7903,7 +7877,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>114</v>
       </c>
       <c r="B52">
@@ -7917,7 +7891,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>115</v>
       </c>
       <c r="B53">
@@ -7931,7 +7905,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>116</v>
       </c>
       <c r="B54">
@@ -7945,7 +7919,7 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>117</v>
       </c>
       <c r="B55">
@@ -7959,7 +7933,7 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>118</v>
       </c>
       <c r="B56">
@@ -7973,7 +7947,7 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>119</v>
       </c>
       <c r="B57">
@@ -7987,7 +7961,7 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>120</v>
       </c>
       <c r="B58">
@@ -8001,7 +7975,7 @@
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>121</v>
       </c>
       <c r="B59">
@@ -8015,7 +7989,7 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>122</v>
       </c>
       <c r="B60">
@@ -8029,7 +8003,7 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>123</v>
       </c>
       <c r="B61">
@@ -8043,7 +8017,7 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>124</v>
       </c>
       <c r="B62">
@@ -8057,7 +8031,7 @@
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>125</v>
       </c>
       <c r="B63">
@@ -8071,7 +8045,7 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>126</v>
       </c>
       <c r="B64">
@@ -8085,7 +8059,7 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>127</v>
       </c>
       <c r="B65">
@@ -8099,7 +8073,7 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>128</v>
       </c>
       <c r="B66">
@@ -8113,7 +8087,7 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>129</v>
       </c>
       <c r="B67">
@@ -8124,7 +8098,7 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>130</v>
       </c>
       <c r="B68">
@@ -8138,7 +8112,7 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>131</v>
       </c>
       <c r="B69">
@@ -8152,7 +8126,7 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>132</v>
       </c>
       <c r="B70">
@@ -8166,7 +8140,7 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>133</v>
       </c>
       <c r="B71">
@@ -8180,7 +8154,7 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>134</v>
       </c>
       <c r="B72">
@@ -8194,7 +8168,7 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>135</v>
       </c>
       <c r="B73">
@@ -8208,7 +8182,7 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>136</v>
       </c>
       <c r="B74">
@@ -8222,7 +8196,7 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>137</v>
       </c>
       <c r="B75">
@@ -8236,7 +8210,7 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>138</v>
       </c>
       <c r="B76">
@@ -8250,7 +8224,7 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>139</v>
       </c>
       <c r="B77">
@@ -8264,7 +8238,7 @@
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>140</v>
       </c>
       <c r="B78">
@@ -8278,7 +8252,7 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>141</v>
       </c>
       <c r="B79">
@@ -8292,7 +8266,7 @@
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>142</v>
       </c>
       <c r="B80">
@@ -8306,7 +8280,7 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>143</v>
       </c>
       <c r="B81">
@@ -8320,7 +8294,7 @@
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>144</v>
       </c>
       <c r="B82">
@@ -8334,7 +8308,7 @@
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>145</v>
       </c>
       <c r="B83">
@@ -8348,7 +8322,7 @@
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>146</v>
       </c>
       <c r="B84">
@@ -8362,7 +8336,7 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>147</v>
       </c>
       <c r="B85">
@@ -8376,7 +8350,7 @@
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>148</v>
       </c>
       <c r="B86">
@@ -8390,7 +8364,7 @@
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>149</v>
       </c>
       <c r="B87">
@@ -8404,7 +8378,7 @@
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>150</v>
       </c>
       <c r="B88">
@@ -8418,7 +8392,7 @@
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>151</v>
       </c>
       <c r="B89">
@@ -8432,7 +8406,7 @@
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>152</v>
       </c>
       <c r="B90">
@@ -8446,7 +8420,7 @@
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>153</v>
       </c>
       <c r="B91">
@@ -8460,7 +8434,7 @@
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>154</v>
       </c>
       <c r="B92">
@@ -8474,7 +8448,7 @@
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>155</v>
       </c>
       <c r="B93">
@@ -8488,7 +8462,7 @@
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>156</v>
       </c>
       <c r="B94">
@@ -8502,7 +8476,7 @@
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>157</v>
       </c>
       <c r="B95">
@@ -8516,7 +8490,7 @@
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>158</v>
       </c>
       <c r="B96">
@@ -8530,7 +8504,7 @@
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>159</v>
       </c>
       <c r="B97">
@@ -8544,7 +8518,7 @@
       </c>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>160</v>
       </c>
       <c r="B98">
@@ -8558,7 +8532,7 @@
       </c>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>161</v>
       </c>
       <c r="B99">
@@ -8572,7 +8546,7 @@
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>162</v>
       </c>
       <c r="B100">
@@ -8586,7 +8560,7 @@
       </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>163</v>
       </c>
       <c r="B101">
@@ -8600,7 +8574,7 @@
       </c>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>164</v>
       </c>
       <c r="B102">
@@ -8614,7 +8588,7 @@
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>165</v>
       </c>
       <c r="B103">
@@ -8628,7 +8602,7 @@
       </c>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>166</v>
       </c>
       <c r="B104">
@@ -8642,7 +8616,7 @@
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>167</v>
       </c>
       <c r="B105">
@@ -8656,7 +8630,7 @@
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>168</v>
       </c>
       <c r="B106">
@@ -8670,7 +8644,7 @@
       </c>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>169</v>
       </c>
       <c r="B107">
@@ -8684,7 +8658,7 @@
       </c>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>170</v>
       </c>
       <c r="B108">
@@ -8698,7 +8672,7 @@
       </c>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>171</v>
       </c>
       <c r="B109">
@@ -8712,7 +8686,7 @@
       </c>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>172</v>
       </c>
       <c r="B110">
@@ -8726,7 +8700,7 @@
       </c>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>173</v>
       </c>
       <c r="B111">
@@ -8740,7 +8714,7 @@
       </c>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>174</v>
       </c>
       <c r="B112">
@@ -8754,7 +8728,7 @@
       </c>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>175</v>
       </c>
       <c r="B113">
@@ -8768,7 +8742,7 @@
       </c>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>176</v>
       </c>
       <c r="B114">
@@ -8782,7 +8756,7 @@
       </c>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>177</v>
       </c>
       <c r="B115">
@@ -8796,7 +8770,7 @@
       </c>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>178</v>
       </c>
       <c r="B116">
@@ -8810,7 +8784,7 @@
       </c>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="1" t="s">
+      <c r="A117" t="s">
         <v>179</v>
       </c>
       <c r="B117">
@@ -8824,7 +8798,7 @@
       </c>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="1" t="s">
+      <c r="A118" t="s">
         <v>180</v>
       </c>
       <c r="B118">
@@ -8838,7 +8812,7 @@
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="1" t="s">
+      <c r="A119" t="s">
         <v>181</v>
       </c>
       <c r="B119">
@@ -8852,7 +8826,7 @@
       </c>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="1" t="s">
+      <c r="A120" t="s">
         <v>182</v>
       </c>
       <c r="B120">
@@ -8866,7 +8840,7 @@
       </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="1" t="s">
+      <c r="A121" t="s">
         <v>183</v>
       </c>
       <c r="B121">
@@ -8880,7 +8854,7 @@
       </c>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="1" t="s">
+      <c r="A122" t="s">
         <v>184</v>
       </c>
       <c r="B122">
@@ -8894,7 +8868,7 @@
       </c>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="1" t="s">
+      <c r="A123" t="s">
         <v>185</v>
       </c>
       <c r="B123">
@@ -8908,7 +8882,7 @@
       </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="1" t="s">
+      <c r="A124" t="s">
         <v>186</v>
       </c>
       <c r="B124">
@@ -8922,7 +8896,7 @@
       </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="1" t="s">
+      <c r="A125" t="s">
         <v>187</v>
       </c>
       <c r="B125">
@@ -8936,7 +8910,7 @@
       </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="1" t="s">
+      <c r="A126" t="s">
         <v>188</v>
       </c>
       <c r="B126">
@@ -8950,7 +8924,7 @@
       </c>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="1" t="s">
+      <c r="A127" t="s">
         <v>189</v>
       </c>
       <c r="B127">
@@ -8964,7 +8938,7 @@
       </c>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
         <v>190</v>
       </c>
       <c r="B128">
@@ -8978,7 +8952,7 @@
       </c>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="1" t="s">
+      <c r="A129" t="s">
         <v>191</v>
       </c>
       <c r="B129">
@@ -8992,7 +8966,7 @@
       </c>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="1" t="s">
+      <c r="A130" t="s">
         <v>192</v>
       </c>
       <c r="B130">
@@ -9006,7 +8980,7 @@
       </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="1" t="s">
+      <c r="A131" t="s">
         <v>193</v>
       </c>
       <c r="B131">
@@ -9020,7 +8994,7 @@
       </c>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="1" t="s">
+      <c r="A132" t="s">
         <v>194</v>
       </c>
       <c r="B132">
@@ -9034,7 +9008,7 @@
       </c>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="1" t="s">
+      <c r="A133" t="s">
         <v>195</v>
       </c>
       <c r="B133">
@@ -9048,7 +9022,7 @@
       </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="1" t="s">
+      <c r="A134" t="s">
         <v>196</v>
       </c>
       <c r="B134">
@@ -9062,7 +9036,7 @@
       </c>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="1" t="s">
+      <c r="A135" t="s">
         <v>197</v>
       </c>
       <c r="B135">
@@ -9076,7 +9050,7 @@
       </c>
     </row>
     <row r="136" spans="1:4">
-      <c r="A136" s="1" t="s">
+      <c r="A136" t="s">
         <v>198</v>
       </c>
       <c r="B136">
@@ -9090,7 +9064,7 @@
       </c>
     </row>
     <row r="137" spans="1:4">
-      <c r="A137" s="1" t="s">
+      <c r="A137" t="s">
         <v>199</v>
       </c>
       <c r="B137">
@@ -9104,7 +9078,7 @@
       </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="1" t="s">
+      <c r="A138" t="s">
         <v>200</v>
       </c>
       <c r="B138">
@@ -9118,7 +9092,7 @@
       </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="1" t="s">
+      <c r="A139" t="s">
         <v>201</v>
       </c>
       <c r="B139">
@@ -9132,7 +9106,7 @@
       </c>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="1" t="s">
+      <c r="A140" t="s">
         <v>202</v>
       </c>
       <c r="B140">
@@ -9146,7 +9120,7 @@
       </c>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="1" t="s">
+      <c r="A141" t="s">
         <v>203</v>
       </c>
       <c r="B141">
@@ -9160,7 +9134,7 @@
       </c>
     </row>
     <row r="142" spans="1:4">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>204</v>
       </c>
       <c r="B142">
@@ -9174,7 +9148,7 @@
       </c>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="1" t="s">
+      <c r="A143" t="s">
         <v>205</v>
       </c>
       <c r="B143">
@@ -9188,7 +9162,7 @@
       </c>
     </row>
     <row r="144" spans="1:4">
-      <c r="A144" s="1" t="s">
+      <c r="A144" t="s">
         <v>206</v>
       </c>
       <c r="B144">
@@ -9202,7 +9176,7 @@
       </c>
     </row>
     <row r="145" spans="1:4">
-      <c r="A145" s="1" t="s">
+      <c r="A145" t="s">
         <v>207</v>
       </c>
       <c r="B145">
@@ -9216,7 +9190,7 @@
       </c>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="1" t="s">
+      <c r="A146" t="s">
         <v>208</v>
       </c>
       <c r="B146">
@@ -9230,7 +9204,7 @@
       </c>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="1" t="s">
+      <c r="A147" t="s">
         <v>209</v>
       </c>
       <c r="B147">
@@ -9244,7 +9218,7 @@
       </c>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="1" t="s">
+      <c r="A148" t="s">
         <v>210</v>
       </c>
       <c r="B148">
@@ -9258,7 +9232,7 @@
       </c>
     </row>
     <row r="149" spans="1:4">
-      <c r="A149" s="1" t="s">
+      <c r="A149" t="s">
         <v>211</v>
       </c>
       <c r="B149">
@@ -9272,7 +9246,7 @@
       </c>
     </row>
     <row r="150" spans="1:4">
-      <c r="A150" s="1" t="s">
+      <c r="A150" t="s">
         <v>212</v>
       </c>
       <c r="B150">
@@ -9286,7 +9260,7 @@
       </c>
     </row>
     <row r="151" spans="1:4">
-      <c r="A151" s="1" t="s">
+      <c r="A151" t="s">
         <v>213</v>
       </c>
       <c r="B151">
@@ -9300,7 +9274,7 @@
       </c>
     </row>
     <row r="152" spans="1:4">
-      <c r="A152" s="1" t="s">
+      <c r="A152" t="s">
         <v>214</v>
       </c>
       <c r="B152">
@@ -9314,7 +9288,7 @@
       </c>
     </row>
     <row r="153" spans="1:4">
-      <c r="A153" s="1" t="s">
+      <c r="A153" t="s">
         <v>215</v>
       </c>
       <c r="B153">
@@ -9328,7 +9302,7 @@
       </c>
     </row>
     <row r="154" spans="1:4">
-      <c r="A154" s="1" t="s">
+      <c r="A154" t="s">
         <v>216</v>
       </c>
       <c r="B154">
@@ -9342,7 +9316,7 @@
       </c>
     </row>
     <row r="155" spans="1:4">
-      <c r="A155" s="1" t="s">
+      <c r="A155" t="s">
         <v>217</v>
       </c>
       <c r="B155">
@@ -9356,7 +9330,7 @@
       </c>
     </row>
     <row r="156" spans="1:4">
-      <c r="A156" s="1" t="s">
+      <c r="A156" t="s">
         <v>218</v>
       </c>
       <c r="B156">
@@ -9370,7 +9344,7 @@
       </c>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="1" t="s">
+      <c r="A157" t="s">
         <v>219</v>
       </c>
       <c r="B157">
@@ -9384,7 +9358,7 @@
       </c>
     </row>
     <row r="158" spans="1:4">
-      <c r="A158" s="1" t="s">
+      <c r="A158" t="s">
         <v>220</v>
       </c>
       <c r="B158">
@@ -9398,7 +9372,7 @@
       </c>
     </row>
     <row r="159" spans="1:4">
-      <c r="A159" s="1" t="s">
+      <c r="A159" t="s">
         <v>221</v>
       </c>
       <c r="B159">
@@ -9412,7 +9386,7 @@
       </c>
     </row>
     <row r="160" spans="1:4">
-      <c r="A160" s="1" t="s">
+      <c r="A160" t="s">
         <v>222</v>
       </c>
       <c r="B160">
@@ -9426,7 +9400,7 @@
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="1" t="s">
+      <c r="A161" t="s">
         <v>223</v>
       </c>
       <c r="B161">
@@ -9440,7 +9414,7 @@
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="1" t="s">
+      <c r="A162" t="s">
         <v>224</v>
       </c>
       <c r="B162">
@@ -9454,7 +9428,7 @@
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="1" t="s">
+      <c r="A163" t="s">
         <v>225</v>
       </c>
       <c r="B163">
@@ -9468,7 +9442,7 @@
       </c>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="1" t="s">
+      <c r="A164" t="s">
         <v>226</v>
       </c>
       <c r="B164">
@@ -9482,7 +9456,7 @@
       </c>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="1" t="s">
+      <c r="A165" t="s">
         <v>227</v>
       </c>
       <c r="B165">
@@ -9496,7 +9470,7 @@
       </c>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="1" t="s">
+      <c r="A166" t="s">
         <v>228</v>
       </c>
       <c r="B166">
@@ -9510,7 +9484,7 @@
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="1" t="s">
+      <c r="A167" t="s">
         <v>229</v>
       </c>
       <c r="B167">
@@ -9524,7 +9498,7 @@
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="1" t="s">
+      <c r="A168" t="s">
         <v>230</v>
       </c>
       <c r="B168">
@@ -9538,7 +9512,7 @@
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="1" t="s">
+      <c r="A169" t="s">
         <v>231</v>
       </c>
       <c r="B169">
@@ -9552,7 +9526,7 @@
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="1" t="s">
+      <c r="A170" t="s">
         <v>232</v>
       </c>
       <c r="B170">
@@ -9566,7 +9540,7 @@
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="1" t="s">
+      <c r="A171" t="s">
         <v>233</v>
       </c>
       <c r="B171">
@@ -9580,7 +9554,7 @@
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="1" t="s">
+      <c r="A172" t="s">
         <v>234</v>
       </c>
       <c r="B172">
@@ -9594,7 +9568,7 @@
       </c>
     </row>
     <row r="173" spans="1:4">
-      <c r="A173" s="1" t="s">
+      <c r="A173" t="s">
         <v>235</v>
       </c>
       <c r="B173">
@@ -9608,7 +9582,7 @@
       </c>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="1" t="s">
+      <c r="A174" t="s">
         <v>236</v>
       </c>
       <c r="B174">
@@ -9622,7 +9596,7 @@
       </c>
     </row>
     <row r="175" spans="1:4">
-      <c r="A175" s="1" t="s">
+      <c r="A175" t="s">
         <v>237</v>
       </c>
       <c r="B175">
@@ -9636,7 +9610,7 @@
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="1" t="s">
+      <c r="A176" t="s">
         <v>238</v>
       </c>
       <c r="B176">
@@ -9650,7 +9624,7 @@
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="1" t="s">
+      <c r="A177" t="s">
         <v>239</v>
       </c>
       <c r="B177">
@@ -9664,7 +9638,7 @@
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="1" t="s">
+      <c r="A178" t="s">
         <v>240</v>
       </c>
       <c r="B178">
@@ -9678,7 +9652,7 @@
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="1" t="s">
+      <c r="A179" t="s">
         <v>241</v>
       </c>
       <c r="B179">
@@ -9692,7 +9666,7 @@
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="1" t="s">
+      <c r="A180" t="s">
         <v>242</v>
       </c>
       <c r="B180">
@@ -9706,7 +9680,7 @@
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="1" t="s">
+      <c r="A181" t="s">
         <v>243</v>
       </c>
       <c r="B181">
@@ -9720,7 +9694,7 @@
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="1" t="s">
+      <c r="A182" t="s">
         <v>244</v>
       </c>
       <c r="B182">
@@ -9734,7 +9708,7 @@
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="1" t="s">
+      <c r="A183" t="s">
         <v>245</v>
       </c>
       <c r="B183">
@@ -9748,7 +9722,7 @@
       </c>
     </row>
     <row r="184" spans="1:4">
-      <c r="A184" s="1" t="s">
+      <c r="A184" t="s">
         <v>246</v>
       </c>
       <c r="B184">
@@ -9762,7 +9736,7 @@
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="1" t="s">
+      <c r="A185" t="s">
         <v>247</v>
       </c>
       <c r="B185">
@@ -9776,7 +9750,7 @@
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="1" t="s">
+      <c r="A186" t="s">
         <v>248</v>
       </c>
       <c r="B186">
@@ -9790,7 +9764,7 @@
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="1" t="s">
+      <c r="A187" t="s">
         <v>249</v>
       </c>
       <c r="B187">
@@ -9804,7 +9778,7 @@
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="1" t="s">
+      <c r="A188" t="s">
         <v>250</v>
       </c>
       <c r="B188">
@@ -9818,7 +9792,7 @@
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="1" t="s">
+      <c r="A189" t="s">
         <v>251</v>
       </c>
       <c r="B189">
@@ -9832,7 +9806,7 @@
       </c>
     </row>
     <row r="190" spans="1:4">
-      <c r="A190" s="1" t="s">
+      <c r="A190" t="s">
         <v>252</v>
       </c>
       <c r="B190">
@@ -9846,7 +9820,7 @@
       </c>
     </row>
     <row r="191" spans="1:4">
-      <c r="A191" s="1" t="s">
+      <c r="A191" t="s">
         <v>253</v>
       </c>
       <c r="B191">
@@ -9860,7 +9834,7 @@
       </c>
     </row>
     <row r="192" spans="1:4">
-      <c r="A192" s="1" t="s">
+      <c r="A192" t="s">
         <v>254</v>
       </c>
       <c r="B192">
@@ -9874,7 +9848,7 @@
       </c>
     </row>
     <row r="193" spans="1:4">
-      <c r="A193" s="1" t="s">
+      <c r="A193" t="s">
         <v>255</v>
       </c>
       <c r="B193">
@@ -9888,7 +9862,7 @@
       </c>
     </row>
     <row r="194" spans="1:4">
-      <c r="A194" s="1" t="s">
+      <c r="A194" t="s">
         <v>256</v>
       </c>
       <c r="B194">
@@ -9902,7 +9876,7 @@
       </c>
     </row>
     <row r="195" spans="1:4">
-      <c r="A195" s="1" t="s">
+      <c r="A195" t="s">
         <v>257</v>
       </c>
       <c r="B195">
@@ -9916,7 +9890,7 @@
       </c>
     </row>
     <row r="196" spans="1:4">
-      <c r="A196" s="1" t="s">
+      <c r="A196" t="s">
         <v>258</v>
       </c>
       <c r="B196">
@@ -9930,7 +9904,7 @@
       </c>
     </row>
     <row r="197" spans="1:4">
-      <c r="A197" s="1" t="s">
+      <c r="A197" t="s">
         <v>259</v>
       </c>
       <c r="B197">
@@ -9944,7 +9918,7 @@
       </c>
     </row>
     <row r="198" spans="1:4">
-      <c r="A198" s="1" t="s">
+      <c r="A198" t="s">
         <v>260</v>
       </c>
       <c r="B198">
@@ -9958,7 +9932,7 @@
       </c>
     </row>
     <row r="199" spans="1:4">
-      <c r="A199" s="1" t="s">
+      <c r="A199" t="s">
         <v>261</v>
       </c>
       <c r="B199">
@@ -9972,7 +9946,7 @@
       </c>
     </row>
     <row r="200" spans="1:4">
-      <c r="A200" s="1" t="s">
+      <c r="A200" t="s">
         <v>262</v>
       </c>
       <c r="B200">
@@ -9986,7 +9960,7 @@
       </c>
     </row>
     <row r="201" spans="1:4">
-      <c r="A201" s="1" t="s">
+      <c r="A201" t="s">
         <v>263</v>
       </c>
       <c r="B201">
@@ -10000,7 +9974,7 @@
       </c>
     </row>
     <row r="202" spans="1:4">
-      <c r="A202" s="1" t="s">
+      <c r="A202" t="s">
         <v>264</v>
       </c>
       <c r="B202">
@@ -10014,7 +9988,7 @@
       </c>
     </row>
     <row r="203" spans="1:4">
-      <c r="A203" s="1" t="s">
+      <c r="A203" t="s">
         <v>265</v>
       </c>
       <c r="B203">
@@ -10028,7 +10002,7 @@
       </c>
     </row>
     <row r="204" spans="1:4">
-      <c r="A204" s="1" t="s">
+      <c r="A204" t="s">
         <v>266</v>
       </c>
       <c r="B204">
@@ -10042,7 +10016,7 @@
       </c>
     </row>
     <row r="205" spans="1:4">
-      <c r="A205" s="1" t="s">
+      <c r="A205" t="s">
         <v>267</v>
       </c>
       <c r="B205">
@@ -10056,7 +10030,7 @@
       </c>
     </row>
     <row r="206" spans="1:4">
-      <c r="A206" s="1" t="s">
+      <c r="A206" t="s">
         <v>268</v>
       </c>
       <c r="B206">
@@ -10070,7 +10044,7 @@
       </c>
     </row>
     <row r="207" spans="1:4">
-      <c r="A207" s="1" t="s">
+      <c r="A207" t="s">
         <v>269</v>
       </c>
       <c r="B207">
@@ -10084,7 +10058,7 @@
       </c>
     </row>
     <row r="208" spans="1:4">
-      <c r="A208" s="1" t="s">
+      <c r="A208" t="s">
         <v>270</v>
       </c>
       <c r="B208">
@@ -10098,7 +10072,7 @@
       </c>
     </row>
     <row r="209" spans="1:4">
-      <c r="A209" s="1" t="s">
+      <c r="A209" t="s">
         <v>271</v>
       </c>
       <c r="B209">
@@ -10112,7 +10086,7 @@
       </c>
     </row>
     <row r="210" spans="1:4">
-      <c r="A210" s="1" t="s">
+      <c r="A210" t="s">
         <v>272</v>
       </c>
       <c r="B210">
@@ -10126,7 +10100,7 @@
       </c>
     </row>
     <row r="211" spans="1:4">
-      <c r="A211" s="1" t="s">
+      <c r="A211" t="s">
         <v>273</v>
       </c>
       <c r="B211">
@@ -10140,7 +10114,7 @@
       </c>
     </row>
     <row r="212" spans="1:4">
-      <c r="A212" s="1" t="s">
+      <c r="A212" t="s">
         <v>274</v>
       </c>
       <c r="B212">
@@ -10154,7 +10128,7 @@
       </c>
     </row>
     <row r="213" spans="1:4">
-      <c r="A213" s="1" t="s">
+      <c r="A213" t="s">
         <v>275</v>
       </c>
       <c r="B213">
@@ -10168,7 +10142,7 @@
       </c>
     </row>
     <row r="214" spans="1:4">
-      <c r="A214" s="1" t="s">
+      <c r="A214" t="s">
         <v>276</v>
       </c>
       <c r="B214">
@@ -10182,7 +10156,7 @@
       </c>
     </row>
     <row r="215" spans="1:4">
-      <c r="A215" s="1" t="s">
+      <c r="A215" t="s">
         <v>277</v>
       </c>
       <c r="B215">
@@ -10196,7 +10170,7 @@
       </c>
     </row>
     <row r="216" spans="1:4">
-      <c r="A216" s="1" t="s">
+      <c r="A216" t="s">
         <v>278</v>
       </c>
       <c r="B216">
@@ -10210,7 +10184,7 @@
       </c>
     </row>
     <row r="217" spans="1:4">
-      <c r="A217" s="1" t="s">
+      <c r="A217" t="s">
         <v>279</v>
       </c>
       <c r="B217">
@@ -10224,7 +10198,7 @@
       </c>
     </row>
     <row r="218" spans="1:4">
-      <c r="A218" s="1" t="s">
+      <c r="A218" t="s">
         <v>280</v>
       </c>
       <c r="B218">
@@ -10238,7 +10212,7 @@
       </c>
     </row>
     <row r="219" spans="1:4">
-      <c r="A219" s="1" t="s">
+      <c r="A219" t="s">
         <v>281</v>
       </c>
       <c r="B219">
@@ -10252,7 +10226,7 @@
       </c>
     </row>
     <row r="220" spans="1:4">
-      <c r="A220" s="1" t="s">
+      <c r="A220" t="s">
         <v>282</v>
       </c>
       <c r="B220">
@@ -10266,7 +10240,7 @@
       </c>
     </row>
     <row r="221" spans="1:4">
-      <c r="A221" s="1" t="s">
+      <c r="A221" t="s">
         <v>283</v>
       </c>
       <c r="B221">
@@ -10280,7 +10254,7 @@
       </c>
     </row>
     <row r="222" spans="1:4">
-      <c r="A222" s="1" t="s">
+      <c r="A222" t="s">
         <v>284</v>
       </c>
       <c r="B222">
@@ -10294,7 +10268,7 @@
       </c>
     </row>
     <row r="223" spans="1:4">
-      <c r="A223" s="1" t="s">
+      <c r="A223" t="s">
         <v>285</v>
       </c>
       <c r="B223">
@@ -10308,7 +10282,7 @@
       </c>
     </row>
     <row r="224" spans="1:4">
-      <c r="A224" s="1" t="s">
+      <c r="A224" t="s">
         <v>286</v>
       </c>
       <c r="B224">
@@ -10322,7 +10296,7 @@
       </c>
     </row>
     <row r="225" spans="1:4">
-      <c r="A225" s="1" t="s">
+      <c r="A225" t="s">
         <v>287</v>
       </c>
       <c r="B225">
@@ -10336,7 +10310,7 @@
       </c>
     </row>
     <row r="226" spans="1:4">
-      <c r="A226" s="1" t="s">
+      <c r="A226" t="s">
         <v>288</v>
       </c>
       <c r="B226">
@@ -10350,7 +10324,7 @@
       </c>
     </row>
     <row r="227" spans="1:4">
-      <c r="A227" s="1" t="s">
+      <c r="A227" t="s">
         <v>289</v>
       </c>
       <c r="B227">
@@ -10364,7 +10338,7 @@
       </c>
     </row>
     <row r="228" spans="1:4">
-      <c r="A228" s="1" t="s">
+      <c r="A228" t="s">
         <v>290</v>
       </c>
       <c r="B228">
@@ -10378,7 +10352,7 @@
       </c>
     </row>
     <row r="229" spans="1:4">
-      <c r="A229" s="1" t="s">
+      <c r="A229" t="s">
         <v>291</v>
       </c>
       <c r="B229">
@@ -10392,7 +10366,7 @@
       </c>
     </row>
     <row r="230" spans="1:4">
-      <c r="A230" s="1" t="s">
+      <c r="A230" t="s">
         <v>292</v>
       </c>
       <c r="B230">
@@ -10406,7 +10380,7 @@
       </c>
     </row>
     <row r="231" spans="1:4">
-      <c r="A231" s="1" t="s">
+      <c r="A231" t="s">
         <v>293</v>
       </c>
       <c r="B231">
@@ -10420,7 +10394,7 @@
       </c>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="1" t="s">
+      <c r="A232" t="s">
         <v>294</v>
       </c>
       <c r="B232">
@@ -10434,7 +10408,7 @@
       </c>
     </row>
     <row r="233" spans="1:4">
-      <c r="A233" s="1" t="s">
+      <c r="A233" t="s">
         <v>295</v>
       </c>
       <c r="B233">
@@ -10448,7 +10422,7 @@
       </c>
     </row>
     <row r="234" spans="1:4">
-      <c r="A234" s="1" t="s">
+      <c r="A234" t="s">
         <v>296</v>
       </c>
       <c r="B234">
@@ -10462,7 +10436,7 @@
       </c>
     </row>
     <row r="235" spans="1:4">
-      <c r="A235" s="1" t="s">
+      <c r="A235" t="s">
         <v>297</v>
       </c>
       <c r="B235">
@@ -10476,7 +10450,7 @@
       </c>
     </row>
     <row r="236" spans="1:4">
-      <c r="A236" s="1" t="s">
+      <c r="A236" t="s">
         <v>298</v>
       </c>
       <c r="B236">
@@ -10490,7 +10464,7 @@
       </c>
     </row>
     <row r="237" spans="1:4">
-      <c r="A237" s="1" t="s">
+      <c r="A237" t="s">
         <v>299</v>
       </c>
       <c r="B237">
@@ -10504,7 +10478,7 @@
       </c>
     </row>
     <row r="238" spans="1:4">
-      <c r="A238" s="1" t="s">
+      <c r="A238" t="s">
         <v>300</v>
       </c>
       <c r="B238">
@@ -10518,7 +10492,7 @@
       </c>
     </row>
     <row r="239" spans="1:4">
-      <c r="A239" s="1" t="s">
+      <c r="A239" t="s">
         <v>301</v>
       </c>
       <c r="B239">
@@ -10532,7 +10506,7 @@
       </c>
     </row>
     <row r="240" spans="1:4">
-      <c r="A240" s="1" t="s">
+      <c r="A240" t="s">
         <v>302</v>
       </c>
       <c r="B240">
@@ -10546,7 +10520,7 @@
       </c>
     </row>
     <row r="241" spans="1:4">
-      <c r="A241" s="1" t="s">
+      <c r="A241" t="s">
         <v>303</v>
       </c>
       <c r="B241">
@@ -10560,7 +10534,7 @@
       </c>
     </row>
     <row r="242" spans="1:4">
-      <c r="A242" s="1" t="s">
+      <c r="A242" t="s">
         <v>304</v>
       </c>
       <c r="B242">
@@ -10574,7 +10548,7 @@
       </c>
     </row>
     <row r="243" spans="1:4">
-      <c r="A243" s="1" t="s">
+      <c r="A243" t="s">
         <v>305</v>
       </c>
       <c r="B243">
@@ -10588,7 +10562,7 @@
       </c>
     </row>
     <row r="244" spans="1:4">
-      <c r="A244" s="1" t="s">
+      <c r="A244" t="s">
         <v>306</v>
       </c>
       <c r="B244">
@@ -10602,7 +10576,7 @@
       </c>
     </row>
     <row r="245" spans="1:4">
-      <c r="A245" s="1" t="s">
+      <c r="A245" t="s">
         <v>307</v>
       </c>
       <c r="B245">
@@ -10616,7 +10590,7 @@
       </c>
     </row>
     <row r="246" spans="1:4">
-      <c r="A246" s="1" t="s">
+      <c r="A246" t="s">
         <v>308</v>
       </c>
       <c r="B246">
@@ -10630,7 +10604,7 @@
       </c>
     </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="1" t="s">
+      <c r="A247" t="s">
         <v>309</v>
       </c>
       <c r="B247">
@@ -10644,7 +10618,7 @@
       </c>
     </row>
     <row r="248" spans="1:4">
-      <c r="A248" s="1" t="s">
+      <c r="A248" t="s">
         <v>310</v>
       </c>
       <c r="B248">
@@ -10658,7 +10632,7 @@
       </c>
     </row>
     <row r="249" spans="1:4">
-      <c r="A249" s="1" t="s">
+      <c r="A249" t="s">
         <v>311</v>
       </c>
       <c r="B249">
@@ -10672,7 +10646,7 @@
       </c>
     </row>
     <row r="250" spans="1:4">
-      <c r="A250" s="1" t="s">
+      <c r="A250" t="s">
         <v>312</v>
       </c>
       <c r="B250">
@@ -10686,7 +10660,7 @@
       </c>
     </row>
     <row r="251" spans="1:4">
-      <c r="A251" s="1" t="s">
+      <c r="A251" t="s">
         <v>313</v>
       </c>
       <c r="B251">
@@ -10700,7 +10674,7 @@
       </c>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="1" t="s">
+      <c r="A252" t="s">
         <v>314</v>
       </c>
       <c r="B252">
@@ -10714,7 +10688,7 @@
       </c>
     </row>
     <row r="253" spans="1:4">
-      <c r="A253" s="1" t="s">
+      <c r="A253" t="s">
         <v>315</v>
       </c>
       <c r="B253">
@@ -10728,7 +10702,7 @@
       </c>
     </row>
     <row r="254" spans="1:4">
-      <c r="A254" s="1" t="s">
+      <c r="A254" t="s">
         <v>316</v>
       </c>
       <c r="C254">
@@ -10736,7 +10710,7 @@
       </c>
     </row>
     <row r="255" spans="1:4">
-      <c r="A255" s="1" t="s">
+      <c r="A255" t="s">
         <v>317</v>
       </c>
       <c r="B255">
@@ -10750,7 +10724,7 @@
       </c>
     </row>
     <row r="256" spans="1:4">
-      <c r="A256" s="1" t="s">
+      <c r="A256" t="s">
         <v>318</v>
       </c>
       <c r="B256">
@@ -10764,7 +10738,7 @@
       </c>
     </row>
     <row r="257" spans="1:4">
-      <c r="A257" s="1" t="s">
+      <c r="A257" t="s">
         <v>319</v>
       </c>
       <c r="B257">
@@ -10778,7 +10752,7 @@
       </c>
     </row>
     <row r="258" spans="1:4">
-      <c r="A258" s="1" t="s">
+      <c r="A258" t="s">
         <v>320</v>
       </c>
       <c r="B258">
@@ -10792,7 +10766,7 @@
       </c>
     </row>
     <row r="259" spans="1:4">
-      <c r="A259" s="1" t="s">
+      <c r="A259" t="s">
         <v>321</v>
       </c>
       <c r="B259">
@@ -10806,7 +10780,7 @@
       </c>
     </row>
     <row r="260" spans="1:4">
-      <c r="A260" s="1" t="s">
+      <c r="A260" t="s">
         <v>322</v>
       </c>
       <c r="B260">
@@ -10817,7 +10791,7 @@
       </c>
     </row>
     <row r="261" spans="1:4">
-      <c r="A261" s="1" t="s">
+      <c r="A261" t="s">
         <v>323</v>
       </c>
       <c r="B261">
@@ -10831,7 +10805,7 @@
       </c>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="1" t="s">
+      <c r="A262" t="s">
         <v>324</v>
       </c>
       <c r="C262">
@@ -10839,7 +10813,7 @@
       </c>
     </row>
     <row r="263" spans="1:4">
-      <c r="A263" s="1" t="s">
+      <c r="A263" t="s">
         <v>325</v>
       </c>
       <c r="B263">
@@ -10853,7 +10827,7 @@
       </c>
     </row>
     <row r="264" spans="1:4">
-      <c r="A264" s="1" t="s">
+      <c r="A264" t="s">
         <v>326</v>
       </c>
       <c r="B264">
@@ -10867,7 +10841,7 @@
       </c>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="1" t="s">
+      <c r="A265" t="s">
         <v>327</v>
       </c>
       <c r="B265">
@@ -10881,7 +10855,7 @@
       </c>
     </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="1" t="s">
+      <c r="A266" t="s">
         <v>328</v>
       </c>
       <c r="B266">
@@ -10895,7 +10869,7 @@
       </c>
     </row>
     <row r="267" spans="1:4">
-      <c r="A267" s="1" t="s">
+      <c r="A267" t="s">
         <v>329</v>
       </c>
       <c r="B267">
@@ -10909,7 +10883,7 @@
       </c>
     </row>
     <row r="268" spans="1:4">
-      <c r="A268" s="1" t="s">
+      <c r="A268" t="s">
         <v>330</v>
       </c>
       <c r="B268">
@@ -10923,7 +10897,7 @@
       </c>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="1" t="s">
+      <c r="A269" t="s">
         <v>331</v>
       </c>
       <c r="B269">
@@ -10937,7 +10911,7 @@
       </c>
     </row>
     <row r="270" spans="1:4">
-      <c r="A270" s="1" t="s">
+      <c r="A270" t="s">
         <v>332</v>
       </c>
       <c r="B270">
@@ -10948,7 +10922,7 @@
       </c>
     </row>
     <row r="271" spans="1:4">
-      <c r="A271" s="1" t="s">
+      <c r="A271" t="s">
         <v>333</v>
       </c>
       <c r="B271">
@@ -10962,7 +10936,7 @@
       </c>
     </row>
     <row r="272" spans="1:4">
-      <c r="A272" s="1" t="s">
+      <c r="A272" t="s">
         <v>334</v>
       </c>
       <c r="B272">
@@ -10976,7 +10950,7 @@
       </c>
     </row>
     <row r="273" spans="1:4">
-      <c r="A273" s="1" t="s">
+      <c r="A273" t="s">
         <v>335</v>
       </c>
       <c r="B273">
@@ -10990,7 +10964,7 @@
       </c>
     </row>
     <row r="274" spans="1:4">
-      <c r="A274" s="1" t="s">
+      <c r="A274" t="s">
         <v>336</v>
       </c>
       <c r="B274">
@@ -11004,7 +10978,7 @@
       </c>
     </row>
     <row r="275" spans="1:4">
-      <c r="A275" s="1" t="s">
+      <c r="A275" t="s">
         <v>337</v>
       </c>
       <c r="B275">
@@ -11018,7 +10992,7 @@
       </c>
     </row>
     <row r="276" spans="1:4">
-      <c r="A276" s="1" t="s">
+      <c r="A276" t="s">
         <v>338</v>
       </c>
       <c r="B276">
@@ -11032,7 +11006,7 @@
       </c>
     </row>
     <row r="277" spans="1:4">
-      <c r="A277" s="1" t="s">
+      <c r="A277" t="s">
         <v>339</v>
       </c>
       <c r="B277">
@@ -11043,7 +11017,7 @@
       </c>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" s="1" t="s">
+      <c r="A278" t="s">
         <v>340</v>
       </c>
       <c r="B278">
@@ -11057,7 +11031,7 @@
       </c>
     </row>
     <row r="279" spans="1:4">
-      <c r="A279" s="1" t="s">
+      <c r="A279" t="s">
         <v>341</v>
       </c>
       <c r="B279">
@@ -11068,7 +11042,7 @@
       </c>
     </row>
     <row r="280" spans="1:4">
-      <c r="A280" s="1" t="s">
+      <c r="A280" t="s">
         <v>342</v>
       </c>
       <c r="B280">
@@ -11082,7 +11056,7 @@
       </c>
     </row>
     <row r="281" spans="1:4">
-      <c r="A281" s="1" t="s">
+      <c r="A281" t="s">
         <v>343</v>
       </c>
       <c r="B281">
@@ -11096,7 +11070,7 @@
       </c>
     </row>
     <row r="282" spans="1:4">
-      <c r="A282" s="1" t="s">
+      <c r="A282" t="s">
         <v>344</v>
       </c>
       <c r="B282">
@@ -11107,7 +11081,7 @@
       </c>
     </row>
     <row r="283" spans="1:4">
-      <c r="A283" s="1" t="s">
+      <c r="A283" t="s">
         <v>345</v>
       </c>
       <c r="B283">
@@ -11121,7 +11095,7 @@
       </c>
     </row>
     <row r="284" spans="1:4">
-      <c r="A284" s="1" t="s">
+      <c r="A284" t="s">
         <v>346</v>
       </c>
       <c r="C284">
@@ -11129,7 +11103,7 @@
       </c>
     </row>
     <row r="285" spans="1:4">
-      <c r="A285" s="1" t="s">
+      <c r="A285" t="s">
         <v>347</v>
       </c>
       <c r="B285">
@@ -11143,7 +11117,7 @@
       </c>
     </row>
     <row r="286" spans="1:4">
-      <c r="A286" s="1" t="s">
+      <c r="A286" t="s">
         <v>348</v>
       </c>
       <c r="B286">
@@ -11157,7 +11131,7 @@
       </c>
     </row>
     <row r="287" spans="1:4">
-      <c r="A287" s="1" t="s">
+      <c r="A287" t="s">
         <v>349</v>
       </c>
       <c r="B287">
@@ -11181,21 +11155,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -11209,7 +11183,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
@@ -11223,7 +11197,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
@@ -11237,7 +11211,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
@@ -11251,7 +11225,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
@@ -11265,7 +11239,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7">
@@ -11279,7 +11253,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
@@ -11303,21 +11277,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -11331,7 +11305,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3">
@@ -11345,7 +11319,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4">
@@ -11359,7 +11333,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5">
@@ -11373,7 +11347,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6">
@@ -11387,7 +11361,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7">
@@ -11401,7 +11375,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8">
@@ -11415,7 +11389,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9">
@@ -11429,7 +11403,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
@@ -11443,7 +11417,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
@@ -11457,7 +11431,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12">
@@ -11471,7 +11445,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
@@ -11485,7 +11459,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14">
@@ -11499,7 +11473,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
       <c r="B15">
@@ -11513,7 +11487,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16">
@@ -11527,7 +11501,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>26</v>
       </c>
       <c r="B17">
@@ -11541,7 +11515,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>27</v>
       </c>
       <c r="B18">
@@ -11555,7 +11529,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19">
@@ -11569,7 +11543,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>29</v>
       </c>
       <c r="B20">
@@ -11583,7 +11557,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>30</v>
       </c>
       <c r="B21">
@@ -11597,7 +11571,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>31</v>
       </c>
       <c r="B22">
@@ -11611,7 +11585,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>32</v>
       </c>
       <c r="B23">
@@ -11625,7 +11599,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24">
@@ -11639,7 +11613,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>34</v>
       </c>
       <c r="B25">
@@ -11653,7 +11627,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>35</v>
       </c>
       <c r="B26">
@@ -11667,7 +11641,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>36</v>
       </c>
       <c r="B27">
@@ -11681,7 +11655,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>37</v>
       </c>
       <c r="B28">
@@ -11695,7 +11669,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>38</v>
       </c>
       <c r="B29">
@@ -11709,7 +11683,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>39</v>
       </c>
       <c r="B30">
@@ -11723,7 +11697,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>40</v>
       </c>
       <c r="B31">
@@ -11737,7 +11711,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>41</v>
       </c>
       <c r="B32">
@@ -11751,7 +11725,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>42</v>
       </c>
       <c r="B33">
@@ -11765,7 +11739,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>43</v>
       </c>
       <c r="B34">
@@ -11779,7 +11753,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>44</v>
       </c>
       <c r="B35">
@@ -11793,7 +11767,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>45</v>
       </c>
       <c r="B36">
@@ -11807,7 +11781,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>46</v>
       </c>
       <c r="B37">
@@ -11821,7 +11795,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>47</v>
       </c>
       <c r="B38">
@@ -11835,7 +11809,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>48</v>
       </c>
       <c r="B39">
@@ -11849,7 +11823,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40">
@@ -11863,7 +11837,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>50</v>
       </c>
       <c r="B41">
@@ -11877,7 +11851,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>51</v>
       </c>
       <c r="B42">
@@ -11891,7 +11865,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>52</v>
       </c>
       <c r="B43">
@@ -11905,7 +11879,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>53</v>
       </c>
       <c r="B44">
@@ -11919,7 +11893,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>54</v>
       </c>
       <c r="B45">
@@ -11933,7 +11907,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>55</v>
       </c>
       <c r="B46">
@@ -11947,7 +11921,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>56</v>
       </c>
       <c r="B47">
@@ -11961,7 +11935,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>57</v>
       </c>
       <c r="B48">
@@ -11975,7 +11949,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>58</v>
       </c>
       <c r="B49">
@@ -11989,7 +11963,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>59</v>
       </c>
       <c r="B50">
@@ -12003,7 +11977,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>60</v>
       </c>
       <c r="B51">
@@ -12017,7 +11991,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>61</v>
       </c>
       <c r="B52">
@@ -12031,7 +12005,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>62</v>
       </c>
       <c r="B53">
@@ -12045,7 +12019,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>63</v>
       </c>
       <c r="B54">
@@ -12069,21 +12043,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
@@ -12097,7 +12071,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>65</v>
       </c>
       <c r="B3">
@@ -12111,7 +12085,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>66</v>
       </c>
       <c r="B4">
@@ -12119,7 +12093,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>67</v>
       </c>
       <c r="B5">
@@ -12133,7 +12107,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>68</v>
       </c>
       <c r="B6">
@@ -12147,7 +12121,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>69</v>
       </c>
       <c r="B7">
@@ -12161,7 +12135,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>70</v>
       </c>
       <c r="B8">
@@ -12175,7 +12149,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>71</v>
       </c>
       <c r="B9">
@@ -12189,7 +12163,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>72</v>
       </c>
       <c r="B10">
@@ -12203,7 +12177,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>73</v>
       </c>
       <c r="B11">
@@ -12217,7 +12191,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>74</v>
       </c>
       <c r="B12">
@@ -12231,7 +12205,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>75</v>
       </c>
       <c r="B13">
@@ -12245,7 +12219,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>76</v>
       </c>
       <c r="B14">
@@ -12259,7 +12233,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>77</v>
       </c>
       <c r="B15">
@@ -12273,7 +12247,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>78</v>
       </c>
       <c r="B16">
@@ -12287,7 +12261,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>79</v>
       </c>
       <c r="B17">
@@ -12301,7 +12275,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>80</v>
       </c>
       <c r="B18">
@@ -12315,7 +12289,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>81</v>
       </c>
       <c r="B19">
@@ -12329,7 +12303,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20">
@@ -12343,7 +12317,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>83</v>
       </c>
       <c r="B21">
@@ -12357,7 +12331,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>84</v>
       </c>
       <c r="B22">
@@ -12371,7 +12345,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>85</v>
       </c>
       <c r="B23">
@@ -12385,7 +12359,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>86</v>
       </c>
       <c r="B24">
@@ -12399,7 +12373,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>87</v>
       </c>
       <c r="B25">
@@ -12413,7 +12387,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>88</v>
       </c>
       <c r="B26">
@@ -12427,7 +12401,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>89</v>
       </c>
       <c r="B27">
@@ -12441,7 +12415,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>90</v>
       </c>
       <c r="B28">
@@ -12455,7 +12429,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>91</v>
       </c>
       <c r="B29">
@@ -12469,7 +12443,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>92</v>
       </c>
       <c r="B30">
@@ -12483,7 +12457,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>93</v>
       </c>
       <c r="B31">
@@ -12497,7 +12471,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>94</v>
       </c>
       <c r="B32">
@@ -12508,7 +12482,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>95</v>
       </c>
       <c r="B33">
@@ -12522,7 +12496,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>96</v>
       </c>
       <c r="B34">
@@ -12536,7 +12510,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>97</v>
       </c>
       <c r="B35">
@@ -12550,7 +12524,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>98</v>
       </c>
       <c r="B36">
@@ -12564,7 +12538,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>99</v>
       </c>
       <c r="B37">
@@ -12578,7 +12552,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>100</v>
       </c>
       <c r="B38">
@@ -12592,7 +12566,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>101</v>
       </c>
       <c r="B39">
@@ -12606,7 +12580,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>102</v>
       </c>
       <c r="B40">
@@ -12620,7 +12594,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>103</v>
       </c>
       <c r="B41">
@@ -12634,7 +12608,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>104</v>
       </c>
       <c r="B42">
@@ -12648,7 +12622,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>105</v>
       </c>
       <c r="B43">
@@ -12662,7 +12636,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>106</v>
       </c>
       <c r="B44">
@@ -12676,7 +12650,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>107</v>
       </c>
       <c r="B45">
@@ -12690,7 +12664,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>108</v>
       </c>
       <c r="B46">
@@ -12704,7 +12678,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>109</v>
       </c>
       <c r="B47">
@@ -12718,7 +12692,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>110</v>
       </c>
       <c r="B48">
@@ -12732,7 +12706,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>111</v>
       </c>
       <c r="B49">
@@ -12746,7 +12720,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>112</v>
       </c>
       <c r="B50">
@@ -12760,7 +12734,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>113</v>
       </c>
       <c r="B51">
@@ -12774,7 +12748,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>114</v>
       </c>
       <c r="B52">
@@ -12788,7 +12762,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>115</v>
       </c>
       <c r="B53">
@@ -12802,7 +12776,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>116</v>
       </c>
       <c r="B54">
@@ -12816,7 +12790,7 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>117</v>
       </c>
       <c r="B55">
@@ -12830,7 +12804,7 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>118</v>
       </c>
       <c r="B56">
@@ -12844,7 +12818,7 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>119</v>
       </c>
       <c r="B57">
@@ -12858,7 +12832,7 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>120</v>
       </c>
       <c r="B58">
@@ -12872,7 +12846,7 @@
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>121</v>
       </c>
       <c r="B59">
@@ -12886,7 +12860,7 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>122</v>
       </c>
       <c r="B60">
@@ -12900,7 +12874,7 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>123</v>
       </c>
       <c r="B61">
@@ -12914,7 +12888,7 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>124</v>
       </c>
       <c r="B62">
@@ -12928,7 +12902,7 @@
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>125</v>
       </c>
       <c r="B63">
@@ -12942,7 +12916,7 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>126</v>
       </c>
       <c r="B64">
@@ -12956,7 +12930,7 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>127</v>
       </c>
       <c r="B65">
@@ -12970,7 +12944,7 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>128</v>
       </c>
       <c r="B66">
@@ -12984,7 +12958,7 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>129</v>
       </c>
       <c r="B67">
@@ -12995,7 +12969,7 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>130</v>
       </c>
       <c r="B68">
@@ -13009,7 +12983,7 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>131</v>
       </c>
       <c r="B69">
@@ -13023,7 +12997,7 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>132</v>
       </c>
       <c r="B70">
@@ -13037,7 +13011,7 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>133</v>
       </c>
       <c r="B71">
@@ -13051,7 +13025,7 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>134</v>
       </c>
       <c r="B72">
@@ -13065,7 +13039,7 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>135</v>
       </c>
       <c r="B73">
@@ -13079,7 +13053,7 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>136</v>
       </c>
       <c r="B74">
@@ -13093,7 +13067,7 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>137</v>
       </c>
       <c r="B75">
@@ -13107,7 +13081,7 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>138</v>
       </c>
       <c r="B76">
@@ -13121,7 +13095,7 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>139</v>
       </c>
       <c r="B77">
@@ -13135,7 +13109,7 @@
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>140</v>
       </c>
       <c r="B78">
@@ -13149,7 +13123,7 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>141</v>
       </c>
       <c r="B79">
@@ -13163,7 +13137,7 @@
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>142</v>
       </c>
       <c r="B80">
@@ -13177,7 +13151,7 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>143</v>
       </c>
       <c r="B81">
@@ -13191,7 +13165,7 @@
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>144</v>
       </c>
       <c r="B82">
@@ -13205,7 +13179,7 @@
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>145</v>
       </c>
       <c r="B83">
@@ -13219,7 +13193,7 @@
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>146</v>
       </c>
       <c r="B84">
@@ -13233,7 +13207,7 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>147</v>
       </c>
       <c r="B85">
@@ -13247,7 +13221,7 @@
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>148</v>
       </c>
       <c r="B86">
@@ -13261,7 +13235,7 @@
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>149</v>
       </c>
       <c r="B87">
@@ -13275,7 +13249,7 @@
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>150</v>
       </c>
       <c r="B88">
@@ -13289,7 +13263,7 @@
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>151</v>
       </c>
       <c r="B89">
@@ -13303,7 +13277,7 @@
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>152</v>
       </c>
       <c r="B90">
@@ -13317,7 +13291,7 @@
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>153</v>
       </c>
       <c r="B91">
@@ -13331,7 +13305,7 @@
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>154</v>
       </c>
       <c r="B92">
@@ -13345,7 +13319,7 @@
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>155</v>
       </c>
       <c r="B93">
@@ -13359,7 +13333,7 @@
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>156</v>
       </c>
       <c r="B94">
@@ -13373,7 +13347,7 @@
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>157</v>
       </c>
       <c r="B95">
@@ -13387,7 +13361,7 @@
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>158</v>
       </c>
       <c r="B96">
@@ -13401,7 +13375,7 @@
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>159</v>
       </c>
       <c r="B97">
@@ -13415,7 +13389,7 @@
       </c>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>160</v>
       </c>
       <c r="B98">
@@ -13429,7 +13403,7 @@
       </c>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>161</v>
       </c>
       <c r="B99">
@@ -13443,7 +13417,7 @@
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>162</v>
       </c>
       <c r="B100">
@@ -13457,7 +13431,7 @@
       </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>163</v>
       </c>
       <c r="B101">
@@ -13471,7 +13445,7 @@
       </c>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>164</v>
       </c>
       <c r="B102">
@@ -13485,7 +13459,7 @@
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>165</v>
       </c>
       <c r="B103">
@@ -13499,7 +13473,7 @@
       </c>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>166</v>
       </c>
       <c r="B104">
@@ -13513,7 +13487,7 @@
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>167</v>
       </c>
       <c r="B105">
@@ -13527,7 +13501,7 @@
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>168</v>
       </c>
       <c r="B106">
@@ -13541,7 +13515,7 @@
       </c>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>169</v>
       </c>
       <c r="B107">
@@ -13555,7 +13529,7 @@
       </c>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>170</v>
       </c>
       <c r="B108">
@@ -13569,7 +13543,7 @@
       </c>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>171</v>
       </c>
       <c r="B109">
@@ -13583,7 +13557,7 @@
       </c>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>172</v>
       </c>
       <c r="B110">
@@ -13597,7 +13571,7 @@
       </c>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>173</v>
       </c>
       <c r="B111">
@@ -13611,7 +13585,7 @@
       </c>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>174</v>
       </c>
       <c r="B112">
@@ -13625,7 +13599,7 @@
       </c>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>175</v>
       </c>
       <c r="B113">
@@ -13639,7 +13613,7 @@
       </c>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>176</v>
       </c>
       <c r="B114">
@@ -13653,7 +13627,7 @@
       </c>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>177</v>
       </c>
       <c r="B115">
@@ -13667,7 +13641,7 @@
       </c>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>178</v>
       </c>
       <c r="B116">
@@ -13681,7 +13655,7 @@
       </c>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="1" t="s">
+      <c r="A117" t="s">
         <v>179</v>
       </c>
       <c r="B117">
@@ -13695,7 +13669,7 @@
       </c>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="1" t="s">
+      <c r="A118" t="s">
         <v>180</v>
       </c>
       <c r="B118">
@@ -13709,7 +13683,7 @@
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="1" t="s">
+      <c r="A119" t="s">
         <v>181</v>
       </c>
       <c r="B119">
@@ -13723,7 +13697,7 @@
       </c>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="1" t="s">
+      <c r="A120" t="s">
         <v>182</v>
       </c>
       <c r="B120">
@@ -13737,7 +13711,7 @@
       </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="1" t="s">
+      <c r="A121" t="s">
         <v>183</v>
       </c>
       <c r="B121">
@@ -13751,7 +13725,7 @@
       </c>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="1" t="s">
+      <c r="A122" t="s">
         <v>184</v>
       </c>
       <c r="B122">
@@ -13765,7 +13739,7 @@
       </c>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="1" t="s">
+      <c r="A123" t="s">
         <v>185</v>
       </c>
       <c r="B123">
@@ -13779,7 +13753,7 @@
       </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="1" t="s">
+      <c r="A124" t="s">
         <v>186</v>
       </c>
       <c r="B124">
@@ -13793,7 +13767,7 @@
       </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="1" t="s">
+      <c r="A125" t="s">
         <v>187</v>
       </c>
       <c r="B125">
@@ -13807,7 +13781,7 @@
       </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="1" t="s">
+      <c r="A126" t="s">
         <v>188</v>
       </c>
       <c r="B126">
@@ -13821,7 +13795,7 @@
       </c>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="1" t="s">
+      <c r="A127" t="s">
         <v>189</v>
       </c>
       <c r="B127">
@@ -13835,7 +13809,7 @@
       </c>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
         <v>190</v>
       </c>
       <c r="B128">
@@ -13849,7 +13823,7 @@
       </c>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="1" t="s">
+      <c r="A129" t="s">
         <v>191</v>
       </c>
       <c r="B129">
@@ -13863,7 +13837,7 @@
       </c>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="1" t="s">
+      <c r="A130" t="s">
         <v>192</v>
       </c>
       <c r="B130">
@@ -13877,7 +13851,7 @@
       </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="1" t="s">
+      <c r="A131" t="s">
         <v>193</v>
       </c>
       <c r="B131">
@@ -13891,7 +13865,7 @@
       </c>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="1" t="s">
+      <c r="A132" t="s">
         <v>194</v>
       </c>
       <c r="B132">
@@ -13905,7 +13879,7 @@
       </c>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="1" t="s">
+      <c r="A133" t="s">
         <v>195</v>
       </c>
       <c r="B133">
@@ -13919,7 +13893,7 @@
       </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="1" t="s">
+      <c r="A134" t="s">
         <v>196</v>
       </c>
       <c r="B134">
@@ -13933,7 +13907,7 @@
       </c>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="1" t="s">
+      <c r="A135" t="s">
         <v>197</v>
       </c>
       <c r="B135">
@@ -13947,7 +13921,7 @@
       </c>
     </row>
     <row r="136" spans="1:4">
-      <c r="A136" s="1" t="s">
+      <c r="A136" t="s">
         <v>198</v>
       </c>
       <c r="B136">
@@ -13961,7 +13935,7 @@
       </c>
     </row>
     <row r="137" spans="1:4">
-      <c r="A137" s="1" t="s">
+      <c r="A137" t="s">
         <v>199</v>
       </c>
       <c r="B137">
@@ -13975,7 +13949,7 @@
       </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="1" t="s">
+      <c r="A138" t="s">
         <v>200</v>
       </c>
       <c r="B138">
@@ -13989,7 +13963,7 @@
       </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="1" t="s">
+      <c r="A139" t="s">
         <v>201</v>
       </c>
       <c r="B139">
@@ -14003,7 +13977,7 @@
       </c>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="1" t="s">
+      <c r="A140" t="s">
         <v>202</v>
       </c>
       <c r="B140">
@@ -14017,7 +13991,7 @@
       </c>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="1" t="s">
+      <c r="A141" t="s">
         <v>203</v>
       </c>
       <c r="B141">
@@ -14031,7 +14005,7 @@
       </c>
     </row>
     <row r="142" spans="1:4">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>204</v>
       </c>
       <c r="B142">
@@ -14045,7 +14019,7 @@
       </c>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="1" t="s">
+      <c r="A143" t="s">
         <v>205</v>
       </c>
       <c r="B143">
@@ -14059,7 +14033,7 @@
       </c>
     </row>
     <row r="144" spans="1:4">
-      <c r="A144" s="1" t="s">
+      <c r="A144" t="s">
         <v>206</v>
       </c>
       <c r="B144">
@@ -14073,7 +14047,7 @@
       </c>
     </row>
     <row r="145" spans="1:4">
-      <c r="A145" s="1" t="s">
+      <c r="A145" t="s">
         <v>207</v>
       </c>
       <c r="B145">
@@ -14087,7 +14061,7 @@
       </c>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="1" t="s">
+      <c r="A146" t="s">
         <v>208</v>
       </c>
       <c r="B146">
@@ -14101,7 +14075,7 @@
       </c>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="1" t="s">
+      <c r="A147" t="s">
         <v>209</v>
       </c>
       <c r="B147">
@@ -14115,7 +14089,7 @@
       </c>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="1" t="s">
+      <c r="A148" t="s">
         <v>210</v>
       </c>
       <c r="B148">
@@ -14129,7 +14103,7 @@
       </c>
     </row>
     <row r="149" spans="1:4">
-      <c r="A149" s="1" t="s">
+      <c r="A149" t="s">
         <v>211</v>
       </c>
       <c r="B149">
@@ -14143,7 +14117,7 @@
       </c>
     </row>
     <row r="150" spans="1:4">
-      <c r="A150" s="1" t="s">
+      <c r="A150" t="s">
         <v>212</v>
       </c>
       <c r="B150">
@@ -14157,7 +14131,7 @@
       </c>
     </row>
     <row r="151" spans="1:4">
-      <c r="A151" s="1" t="s">
+      <c r="A151" t="s">
         <v>213</v>
       </c>
       <c r="B151">
@@ -14171,7 +14145,7 @@
       </c>
     </row>
     <row r="152" spans="1:4">
-      <c r="A152" s="1" t="s">
+      <c r="A152" t="s">
         <v>214</v>
       </c>
       <c r="B152">
@@ -14185,7 +14159,7 @@
       </c>
     </row>
     <row r="153" spans="1:4">
-      <c r="A153" s="1" t="s">
+      <c r="A153" t="s">
         <v>215</v>
       </c>
       <c r="B153">
@@ -14199,7 +14173,7 @@
       </c>
     </row>
     <row r="154" spans="1:4">
-      <c r="A154" s="1" t="s">
+      <c r="A154" t="s">
         <v>216</v>
       </c>
       <c r="B154">
@@ -14213,7 +14187,7 @@
       </c>
     </row>
     <row r="155" spans="1:4">
-      <c r="A155" s="1" t="s">
+      <c r="A155" t="s">
         <v>217</v>
       </c>
       <c r="B155">
@@ -14227,7 +14201,7 @@
       </c>
     </row>
     <row r="156" spans="1:4">
-      <c r="A156" s="1" t="s">
+      <c r="A156" t="s">
         <v>218</v>
       </c>
       <c r="B156">
@@ -14241,7 +14215,7 @@
       </c>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="1" t="s">
+      <c r="A157" t="s">
         <v>219</v>
       </c>
       <c r="B157">
@@ -14255,7 +14229,7 @@
       </c>
     </row>
     <row r="158" spans="1:4">
-      <c r="A158" s="1" t="s">
+      <c r="A158" t="s">
         <v>220</v>
       </c>
       <c r="B158">
@@ -14269,7 +14243,7 @@
       </c>
     </row>
     <row r="159" spans="1:4">
-      <c r="A159" s="1" t="s">
+      <c r="A159" t="s">
         <v>221</v>
       </c>
       <c r="B159">
@@ -14283,7 +14257,7 @@
       </c>
     </row>
     <row r="160" spans="1:4">
-      <c r="A160" s="1" t="s">
+      <c r="A160" t="s">
         <v>222</v>
       </c>
       <c r="B160">
@@ -14297,7 +14271,7 @@
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="1" t="s">
+      <c r="A161" t="s">
         <v>223</v>
       </c>
       <c r="B161">
@@ -14311,7 +14285,7 @@
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="1" t="s">
+      <c r="A162" t="s">
         <v>224</v>
       </c>
       <c r="B162">
@@ -14325,7 +14299,7 @@
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="1" t="s">
+      <c r="A163" t="s">
         <v>225</v>
       </c>
       <c r="B163">
@@ -14339,7 +14313,7 @@
       </c>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="1" t="s">
+      <c r="A164" t="s">
         <v>226</v>
       </c>
       <c r="B164">
@@ -14353,7 +14327,7 @@
       </c>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="1" t="s">
+      <c r="A165" t="s">
         <v>227</v>
       </c>
       <c r="B165">
@@ -14367,7 +14341,7 @@
       </c>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="1" t="s">
+      <c r="A166" t="s">
         <v>228</v>
       </c>
       <c r="B166">
@@ -14381,7 +14355,7 @@
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="1" t="s">
+      <c r="A167" t="s">
         <v>229</v>
       </c>
       <c r="B167">
@@ -14395,7 +14369,7 @@
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="1" t="s">
+      <c r="A168" t="s">
         <v>230</v>
       </c>
       <c r="B168">
@@ -14409,7 +14383,7 @@
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="1" t="s">
+      <c r="A169" t="s">
         <v>231</v>
       </c>
       <c r="B169">
@@ -14423,7 +14397,7 @@
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="1" t="s">
+      <c r="A170" t="s">
         <v>232</v>
       </c>
       <c r="B170">
@@ -14437,7 +14411,7 @@
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="1" t="s">
+      <c r="A171" t="s">
         <v>233</v>
       </c>
       <c r="B171">
@@ -14451,7 +14425,7 @@
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="1" t="s">
+      <c r="A172" t="s">
         <v>234</v>
       </c>
       <c r="B172">
@@ -14465,7 +14439,7 @@
       </c>
     </row>
     <row r="173" spans="1:4">
-      <c r="A173" s="1" t="s">
+      <c r="A173" t="s">
         <v>235</v>
       </c>
       <c r="B173">
@@ -14479,7 +14453,7 @@
       </c>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="1" t="s">
+      <c r="A174" t="s">
         <v>236</v>
       </c>
       <c r="B174">
@@ -14493,7 +14467,7 @@
       </c>
     </row>
     <row r="175" spans="1:4">
-      <c r="A175" s="1" t="s">
+      <c r="A175" t="s">
         <v>237</v>
       </c>
       <c r="B175">
@@ -14507,7 +14481,7 @@
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="1" t="s">
+      <c r="A176" t="s">
         <v>238</v>
       </c>
       <c r="B176">
@@ -14521,7 +14495,7 @@
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="1" t="s">
+      <c r="A177" t="s">
         <v>239</v>
       </c>
       <c r="B177">
@@ -14535,7 +14509,7 @@
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="1" t="s">
+      <c r="A178" t="s">
         <v>240</v>
       </c>
       <c r="B178">
@@ -14549,7 +14523,7 @@
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="1" t="s">
+      <c r="A179" t="s">
         <v>241</v>
       </c>
       <c r="B179">
@@ -14563,7 +14537,7 @@
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="1" t="s">
+      <c r="A180" t="s">
         <v>242</v>
       </c>
       <c r="B180">
@@ -14577,7 +14551,7 @@
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="1" t="s">
+      <c r="A181" t="s">
         <v>243</v>
       </c>
       <c r="B181">
@@ -14591,7 +14565,7 @@
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="1" t="s">
+      <c r="A182" t="s">
         <v>244</v>
       </c>
       <c r="B182">
@@ -14605,7 +14579,7 @@
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="1" t="s">
+      <c r="A183" t="s">
         <v>245</v>
       </c>
       <c r="B183">
@@ -14619,7 +14593,7 @@
       </c>
     </row>
     <row r="184" spans="1:4">
-      <c r="A184" s="1" t="s">
+      <c r="A184" t="s">
         <v>246</v>
       </c>
       <c r="B184">
@@ -14633,7 +14607,7 @@
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="1" t="s">
+      <c r="A185" t="s">
         <v>247</v>
       </c>
       <c r="B185">
@@ -14647,7 +14621,7 @@
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="1" t="s">
+      <c r="A186" t="s">
         <v>248</v>
       </c>
       <c r="B186">
@@ -14661,7 +14635,7 @@
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="1" t="s">
+      <c r="A187" t="s">
         <v>249</v>
       </c>
       <c r="B187">
@@ -14675,7 +14649,7 @@
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="1" t="s">
+      <c r="A188" t="s">
         <v>250</v>
       </c>
       <c r="B188">
@@ -14689,7 +14663,7 @@
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="1" t="s">
+      <c r="A189" t="s">
         <v>251</v>
       </c>
       <c r="B189">
@@ -14703,7 +14677,7 @@
       </c>
     </row>
     <row r="190" spans="1:4">
-      <c r="A190" s="1" t="s">
+      <c r="A190" t="s">
         <v>252</v>
       </c>
       <c r="B190">
@@ -14717,7 +14691,7 @@
       </c>
     </row>
     <row r="191" spans="1:4">
-      <c r="A191" s="1" t="s">
+      <c r="A191" t="s">
         <v>253</v>
       </c>
       <c r="B191">
@@ -14731,7 +14705,7 @@
       </c>
     </row>
     <row r="192" spans="1:4">
-      <c r="A192" s="1" t="s">
+      <c r="A192" t="s">
         <v>254</v>
       </c>
       <c r="B192">
@@ -14745,7 +14719,7 @@
       </c>
     </row>
     <row r="193" spans="1:4">
-      <c r="A193" s="1" t="s">
+      <c r="A193" t="s">
         <v>255</v>
       </c>
       <c r="B193">
@@ -14759,7 +14733,7 @@
       </c>
     </row>
     <row r="194" spans="1:4">
-      <c r="A194" s="1" t="s">
+      <c r="A194" t="s">
         <v>256</v>
       </c>
       <c r="B194">
@@ -14773,7 +14747,7 @@
       </c>
     </row>
     <row r="195" spans="1:4">
-      <c r="A195" s="1" t="s">
+      <c r="A195" t="s">
         <v>257</v>
       </c>
       <c r="B195">
@@ -14787,7 +14761,7 @@
       </c>
     </row>
     <row r="196" spans="1:4">
-      <c r="A196" s="1" t="s">
+      <c r="A196" t="s">
         <v>258</v>
       </c>
       <c r="B196">
@@ -14801,7 +14775,7 @@
       </c>
     </row>
     <row r="197" spans="1:4">
-      <c r="A197" s="1" t="s">
+      <c r="A197" t="s">
         <v>259</v>
       </c>
       <c r="B197">
@@ -14815,7 +14789,7 @@
       </c>
     </row>
     <row r="198" spans="1:4">
-      <c r="A198" s="1" t="s">
+      <c r="A198" t="s">
         <v>260</v>
       </c>
       <c r="B198">
@@ -14829,7 +14803,7 @@
       </c>
     </row>
     <row r="199" spans="1:4">
-      <c r="A199" s="1" t="s">
+      <c r="A199" t="s">
         <v>261</v>
       </c>
       <c r="B199">
@@ -14843,7 +14817,7 @@
       </c>
     </row>
     <row r="200" spans="1:4">
-      <c r="A200" s="1" t="s">
+      <c r="A200" t="s">
         <v>262</v>
       </c>
       <c r="B200">
@@ -14857,7 +14831,7 @@
       </c>
     </row>
     <row r="201" spans="1:4">
-      <c r="A201" s="1" t="s">
+      <c r="A201" t="s">
         <v>263</v>
       </c>
       <c r="B201">
@@ -14871,7 +14845,7 @@
       </c>
     </row>
     <row r="202" spans="1:4">
-      <c r="A202" s="1" t="s">
+      <c r="A202" t="s">
         <v>264</v>
       </c>
       <c r="B202">
@@ -14885,7 +14859,7 @@
       </c>
     </row>
     <row r="203" spans="1:4">
-      <c r="A203" s="1" t="s">
+      <c r="A203" t="s">
         <v>265</v>
       </c>
       <c r="B203">
@@ -14899,7 +14873,7 @@
       </c>
     </row>
     <row r="204" spans="1:4">
-      <c r="A204" s="1" t="s">
+      <c r="A204" t="s">
         <v>266</v>
       </c>
       <c r="B204">
@@ -14913,7 +14887,7 @@
       </c>
     </row>
     <row r="205" spans="1:4">
-      <c r="A205" s="1" t="s">
+      <c r="A205" t="s">
         <v>267</v>
       </c>
       <c r="B205">
@@ -14927,7 +14901,7 @@
       </c>
     </row>
     <row r="206" spans="1:4">
-      <c r="A206" s="1" t="s">
+      <c r="A206" t="s">
         <v>268</v>
       </c>
       <c r="B206">
@@ -14941,7 +14915,7 @@
       </c>
     </row>
     <row r="207" spans="1:4">
-      <c r="A207" s="1" t="s">
+      <c r="A207" t="s">
         <v>269</v>
       </c>
       <c r="B207">
@@ -14955,7 +14929,7 @@
       </c>
     </row>
     <row r="208" spans="1:4">
-      <c r="A208" s="1" t="s">
+      <c r="A208" t="s">
         <v>270</v>
       </c>
       <c r="B208">
@@ -14969,7 +14943,7 @@
       </c>
     </row>
     <row r="209" spans="1:4">
-      <c r="A209" s="1" t="s">
+      <c r="A209" t="s">
         <v>271</v>
       </c>
       <c r="B209">
@@ -14983,7 +14957,7 @@
       </c>
     </row>
     <row r="210" spans="1:4">
-      <c r="A210" s="1" t="s">
+      <c r="A210" t="s">
         <v>272</v>
       </c>
       <c r="B210">
@@ -14997,7 +14971,7 @@
       </c>
     </row>
     <row r="211" spans="1:4">
-      <c r="A211" s="1" t="s">
+      <c r="A211" t="s">
         <v>273</v>
       </c>
       <c r="B211">
@@ -15011,7 +14985,7 @@
       </c>
     </row>
     <row r="212" spans="1:4">
-      <c r="A212" s="1" t="s">
+      <c r="A212" t="s">
         <v>274</v>
       </c>
       <c r="B212">
@@ -15025,7 +14999,7 @@
       </c>
     </row>
     <row r="213" spans="1:4">
-      <c r="A213" s="1" t="s">
+      <c r="A213" t="s">
         <v>275</v>
       </c>
       <c r="B213">
@@ -15039,7 +15013,7 @@
       </c>
     </row>
     <row r="214" spans="1:4">
-      <c r="A214" s="1" t="s">
+      <c r="A214" t="s">
         <v>276</v>
       </c>
       <c r="B214">
@@ -15053,7 +15027,7 @@
       </c>
     </row>
     <row r="215" spans="1:4">
-      <c r="A215" s="1" t="s">
+      <c r="A215" t="s">
         <v>277</v>
       </c>
       <c r="B215">
@@ -15067,7 +15041,7 @@
       </c>
     </row>
     <row r="216" spans="1:4">
-      <c r="A216" s="1" t="s">
+      <c r="A216" t="s">
         <v>278</v>
       </c>
       <c r="B216">
@@ -15081,7 +15055,7 @@
       </c>
     </row>
     <row r="217" spans="1:4">
-      <c r="A217" s="1" t="s">
+      <c r="A217" t="s">
         <v>279</v>
       </c>
       <c r="B217">
@@ -15095,7 +15069,7 @@
       </c>
     </row>
     <row r="218" spans="1:4">
-      <c r="A218" s="1" t="s">
+      <c r="A218" t="s">
         <v>280</v>
       </c>
       <c r="B218">
@@ -15109,7 +15083,7 @@
       </c>
     </row>
     <row r="219" spans="1:4">
-      <c r="A219" s="1" t="s">
+      <c r="A219" t="s">
         <v>281</v>
       </c>
       <c r="B219">
@@ -15123,7 +15097,7 @@
       </c>
     </row>
     <row r="220" spans="1:4">
-      <c r="A220" s="1" t="s">
+      <c r="A220" t="s">
         <v>282</v>
       </c>
       <c r="B220">
@@ -15137,7 +15111,7 @@
       </c>
     </row>
     <row r="221" spans="1:4">
-      <c r="A221" s="1" t="s">
+      <c r="A221" t="s">
         <v>283</v>
       </c>
       <c r="B221">
@@ -15151,7 +15125,7 @@
       </c>
     </row>
     <row r="222" spans="1:4">
-      <c r="A222" s="1" t="s">
+      <c r="A222" t="s">
         <v>284</v>
       </c>
       <c r="B222">
@@ -15165,7 +15139,7 @@
       </c>
     </row>
     <row r="223" spans="1:4">
-      <c r="A223" s="1" t="s">
+      <c r="A223" t="s">
         <v>285</v>
       </c>
       <c r="B223">
@@ -15179,7 +15153,7 @@
       </c>
     </row>
     <row r="224" spans="1:4">
-      <c r="A224" s="1" t="s">
+      <c r="A224" t="s">
         <v>286</v>
       </c>
       <c r="B224">
@@ -15193,7 +15167,7 @@
       </c>
     </row>
     <row r="225" spans="1:4">
-      <c r="A225" s="1" t="s">
+      <c r="A225" t="s">
         <v>287</v>
       </c>
       <c r="B225">
@@ -15207,7 +15181,7 @@
       </c>
     </row>
     <row r="226" spans="1:4">
-      <c r="A226" s="1" t="s">
+      <c r="A226" t="s">
         <v>288</v>
       </c>
       <c r="B226">
@@ -15221,7 +15195,7 @@
       </c>
     </row>
     <row r="227" spans="1:4">
-      <c r="A227" s="1" t="s">
+      <c r="A227" t="s">
         <v>289</v>
       </c>
       <c r="B227">
@@ -15235,7 +15209,7 @@
       </c>
     </row>
     <row r="228" spans="1:4">
-      <c r="A228" s="1" t="s">
+      <c r="A228" t="s">
         <v>290</v>
       </c>
       <c r="B228">
@@ -15249,7 +15223,7 @@
       </c>
     </row>
     <row r="229" spans="1:4">
-      <c r="A229" s="1" t="s">
+      <c r="A229" t="s">
         <v>291</v>
       </c>
       <c r="B229">
@@ -15263,7 +15237,7 @@
       </c>
     </row>
     <row r="230" spans="1:4">
-      <c r="A230" s="1" t="s">
+      <c r="A230" t="s">
         <v>292</v>
       </c>
       <c r="B230">
@@ -15277,7 +15251,7 @@
       </c>
     </row>
     <row r="231" spans="1:4">
-      <c r="A231" s="1" t="s">
+      <c r="A231" t="s">
         <v>293</v>
       </c>
       <c r="B231">
@@ -15291,7 +15265,7 @@
       </c>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="1" t="s">
+      <c r="A232" t="s">
         <v>294</v>
       </c>
       <c r="B232">
@@ -15305,7 +15279,7 @@
       </c>
     </row>
     <row r="233" spans="1:4">
-      <c r="A233" s="1" t="s">
+      <c r="A233" t="s">
         <v>295</v>
       </c>
       <c r="B233">
@@ -15319,7 +15293,7 @@
       </c>
     </row>
     <row r="234" spans="1:4">
-      <c r="A234" s="1" t="s">
+      <c r="A234" t="s">
         <v>296</v>
       </c>
       <c r="B234">
@@ -15333,7 +15307,7 @@
       </c>
     </row>
     <row r="235" spans="1:4">
-      <c r="A235" s="1" t="s">
+      <c r="A235" t="s">
         <v>297</v>
       </c>
       <c r="B235">
@@ -15347,7 +15321,7 @@
       </c>
     </row>
     <row r="236" spans="1:4">
-      <c r="A236" s="1" t="s">
+      <c r="A236" t="s">
         <v>298</v>
       </c>
       <c r="B236">
@@ -15361,7 +15335,7 @@
       </c>
     </row>
     <row r="237" spans="1:4">
-      <c r="A237" s="1" t="s">
+      <c r="A237" t="s">
         <v>299</v>
       </c>
       <c r="B237">
@@ -15375,7 +15349,7 @@
       </c>
     </row>
     <row r="238" spans="1:4">
-      <c r="A238" s="1" t="s">
+      <c r="A238" t="s">
         <v>300</v>
       </c>
       <c r="B238">
@@ -15389,7 +15363,7 @@
       </c>
     </row>
     <row r="239" spans="1:4">
-      <c r="A239" s="1" t="s">
+      <c r="A239" t="s">
         <v>301</v>
       </c>
       <c r="B239">
@@ -15403,7 +15377,7 @@
       </c>
     </row>
     <row r="240" spans="1:4">
-      <c r="A240" s="1" t="s">
+      <c r="A240" t="s">
         <v>302</v>
       </c>
       <c r="B240">
@@ -15417,7 +15391,7 @@
       </c>
     </row>
     <row r="241" spans="1:4">
-      <c r="A241" s="1" t="s">
+      <c r="A241" t="s">
         <v>303</v>
       </c>
       <c r="B241">
@@ -15431,7 +15405,7 @@
       </c>
     </row>
     <row r="242" spans="1:4">
-      <c r="A242" s="1" t="s">
+      <c r="A242" t="s">
         <v>304</v>
       </c>
       <c r="B242">
@@ -15445,7 +15419,7 @@
       </c>
     </row>
     <row r="243" spans="1:4">
-      <c r="A243" s="1" t="s">
+      <c r="A243" t="s">
         <v>305</v>
       </c>
       <c r="B243">
@@ -15459,7 +15433,7 @@
       </c>
     </row>
     <row r="244" spans="1:4">
-      <c r="A244" s="1" t="s">
+      <c r="A244" t="s">
         <v>306</v>
       </c>
       <c r="B244">
@@ -15473,7 +15447,7 @@
       </c>
     </row>
     <row r="245" spans="1:4">
-      <c r="A245" s="1" t="s">
+      <c r="A245" t="s">
         <v>307</v>
       </c>
       <c r="B245">
@@ -15487,7 +15461,7 @@
       </c>
     </row>
     <row r="246" spans="1:4">
-      <c r="A246" s="1" t="s">
+      <c r="A246" t="s">
         <v>308</v>
       </c>
       <c r="B246">
@@ -15501,7 +15475,7 @@
       </c>
     </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="1" t="s">
+      <c r="A247" t="s">
         <v>309</v>
       </c>
       <c r="B247">
@@ -15515,7 +15489,7 @@
       </c>
     </row>
     <row r="248" spans="1:4">
-      <c r="A248" s="1" t="s">
+      <c r="A248" t="s">
         <v>310</v>
       </c>
       <c r="B248">
@@ -15529,7 +15503,7 @@
       </c>
     </row>
     <row r="249" spans="1:4">
-      <c r="A249" s="1" t="s">
+      <c r="A249" t="s">
         <v>311</v>
       </c>
       <c r="B249">
@@ -15543,7 +15517,7 @@
       </c>
     </row>
     <row r="250" spans="1:4">
-      <c r="A250" s="1" t="s">
+      <c r="A250" t="s">
         <v>312</v>
       </c>
       <c r="B250">
@@ -15557,7 +15531,7 @@
       </c>
     </row>
     <row r="251" spans="1:4">
-      <c r="A251" s="1" t="s">
+      <c r="A251" t="s">
         <v>313</v>
       </c>
       <c r="B251">
@@ -15571,7 +15545,7 @@
       </c>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="1" t="s">
+      <c r="A252" t="s">
         <v>314</v>
       </c>
       <c r="B252">
@@ -15585,7 +15559,7 @@
       </c>
     </row>
     <row r="253" spans="1:4">
-      <c r="A253" s="1" t="s">
+      <c r="A253" t="s">
         <v>315</v>
       </c>
       <c r="B253">
@@ -15599,7 +15573,7 @@
       </c>
     </row>
     <row r="254" spans="1:4">
-      <c r="A254" s="1" t="s">
+      <c r="A254" t="s">
         <v>316</v>
       </c>
       <c r="C254">
@@ -15607,7 +15581,7 @@
       </c>
     </row>
     <row r="255" spans="1:4">
-      <c r="A255" s="1" t="s">
+      <c r="A255" t="s">
         <v>317</v>
       </c>
       <c r="B255">
@@ -15618,7 +15592,7 @@
       </c>
     </row>
     <row r="256" spans="1:4">
-      <c r="A256" s="1" t="s">
+      <c r="A256" t="s">
         <v>318</v>
       </c>
       <c r="B256">
@@ -15632,7 +15606,7 @@
       </c>
     </row>
     <row r="257" spans="1:4">
-      <c r="A257" s="1" t="s">
+      <c r="A257" t="s">
         <v>319</v>
       </c>
       <c r="B257">
@@ -15646,7 +15620,7 @@
       </c>
     </row>
     <row r="258" spans="1:4">
-      <c r="A258" s="1" t="s">
+      <c r="A258" t="s">
         <v>320</v>
       </c>
       <c r="B258">
@@ -15660,7 +15634,7 @@
       </c>
     </row>
     <row r="259" spans="1:4">
-      <c r="A259" s="1" t="s">
+      <c r="A259" t="s">
         <v>321</v>
       </c>
       <c r="B259">
@@ -15674,7 +15648,7 @@
       </c>
     </row>
     <row r="260" spans="1:4">
-      <c r="A260" s="1" t="s">
+      <c r="A260" t="s">
         <v>322</v>
       </c>
       <c r="B260">
@@ -15688,7 +15662,7 @@
       </c>
     </row>
     <row r="261" spans="1:4">
-      <c r="A261" s="1" t="s">
+      <c r="A261" t="s">
         <v>323</v>
       </c>
       <c r="B261">
@@ -15702,7 +15676,7 @@
       </c>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="1" t="s">
+      <c r="A262" t="s">
         <v>324</v>
       </c>
       <c r="C262">
@@ -15710,7 +15684,7 @@
       </c>
     </row>
     <row r="263" spans="1:4">
-      <c r="A263" s="1" t="s">
+      <c r="A263" t="s">
         <v>325</v>
       </c>
       <c r="B263">
@@ -15724,7 +15698,7 @@
       </c>
     </row>
     <row r="264" spans="1:4">
-      <c r="A264" s="1" t="s">
+      <c r="A264" t="s">
         <v>326</v>
       </c>
       <c r="B264">
@@ -15738,7 +15712,7 @@
       </c>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="1" t="s">
+      <c r="A265" t="s">
         <v>327</v>
       </c>
       <c r="B265">
@@ -15752,7 +15726,7 @@
       </c>
     </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="1" t="s">
+      <c r="A266" t="s">
         <v>328</v>
       </c>
       <c r="B266">
@@ -15766,7 +15740,7 @@
       </c>
     </row>
     <row r="267" spans="1:4">
-      <c r="A267" s="1" t="s">
+      <c r="A267" t="s">
         <v>329</v>
       </c>
       <c r="B267">
@@ -15780,7 +15754,7 @@
       </c>
     </row>
     <row r="268" spans="1:4">
-      <c r="A268" s="1" t="s">
+      <c r="A268" t="s">
         <v>330</v>
       </c>
       <c r="B268">
@@ -15794,7 +15768,7 @@
       </c>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="1" t="s">
+      <c r="A269" t="s">
         <v>331</v>
       </c>
       <c r="B269">
@@ -15808,7 +15782,7 @@
       </c>
     </row>
     <row r="270" spans="1:4">
-      <c r="A270" s="1" t="s">
+      <c r="A270" t="s">
         <v>332</v>
       </c>
       <c r="B270">
@@ -15822,7 +15796,7 @@
       </c>
     </row>
     <row r="271" spans="1:4">
-      <c r="A271" s="1" t="s">
+      <c r="A271" t="s">
         <v>333</v>
       </c>
       <c r="B271">
@@ -15836,7 +15810,7 @@
       </c>
     </row>
     <row r="272" spans="1:4">
-      <c r="A272" s="1" t="s">
+      <c r="A272" t="s">
         <v>334</v>
       </c>
       <c r="B272">
@@ -15850,7 +15824,7 @@
       </c>
     </row>
     <row r="273" spans="1:4">
-      <c r="A273" s="1" t="s">
+      <c r="A273" t="s">
         <v>335</v>
       </c>
       <c r="B273">
@@ -15864,7 +15838,7 @@
       </c>
     </row>
     <row r="274" spans="1:4">
-      <c r="A274" s="1" t="s">
+      <c r="A274" t="s">
         <v>336</v>
       </c>
       <c r="B274">
@@ -15878,7 +15852,7 @@
       </c>
     </row>
     <row r="275" spans="1:4">
-      <c r="A275" s="1" t="s">
+      <c r="A275" t="s">
         <v>337</v>
       </c>
       <c r="B275">
@@ -15892,7 +15866,7 @@
       </c>
     </row>
     <row r="276" spans="1:4">
-      <c r="A276" s="1" t="s">
+      <c r="A276" t="s">
         <v>338</v>
       </c>
       <c r="B276">
@@ -15906,7 +15880,7 @@
       </c>
     </row>
     <row r="277" spans="1:4">
-      <c r="A277" s="1" t="s">
+      <c r="A277" t="s">
         <v>339</v>
       </c>
       <c r="B277">
@@ -15920,7 +15894,7 @@
       </c>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" s="1" t="s">
+      <c r="A278" t="s">
         <v>340</v>
       </c>
       <c r="B278">
@@ -15934,7 +15908,7 @@
       </c>
     </row>
     <row r="279" spans="1:4">
-      <c r="A279" s="1" t="s">
+      <c r="A279" t="s">
         <v>341</v>
       </c>
       <c r="B279">
@@ -15945,7 +15919,7 @@
       </c>
     </row>
     <row r="280" spans="1:4">
-      <c r="A280" s="1" t="s">
+      <c r="A280" t="s">
         <v>342</v>
       </c>
       <c r="B280">
@@ -15959,7 +15933,7 @@
       </c>
     </row>
     <row r="281" spans="1:4">
-      <c r="A281" s="1" t="s">
+      <c r="A281" t="s">
         <v>343</v>
       </c>
       <c r="B281">
@@ -15973,7 +15947,7 @@
       </c>
     </row>
     <row r="282" spans="1:4">
-      <c r="A282" s="1" t="s">
+      <c r="A282" t="s">
         <v>344</v>
       </c>
       <c r="B282">
@@ -15984,7 +15958,7 @@
       </c>
     </row>
     <row r="283" spans="1:4">
-      <c r="A283" s="1" t="s">
+      <c r="A283" t="s">
         <v>345</v>
       </c>
       <c r="B283">
@@ -15998,7 +15972,7 @@
       </c>
     </row>
     <row r="284" spans="1:4">
-      <c r="A284" s="1" t="s">
+      <c r="A284" t="s">
         <v>346</v>
       </c>
       <c r="C284">
@@ -16006,7 +15980,7 @@
       </c>
     </row>
     <row r="285" spans="1:4">
-      <c r="A285" s="1" t="s">
+      <c r="A285" t="s">
         <v>347</v>
       </c>
       <c r="B285">
@@ -16020,7 +15994,7 @@
       </c>
     </row>
     <row r="286" spans="1:4">
-      <c r="A286" s="1" t="s">
+      <c r="A286" t="s">
         <v>348</v>
       </c>
       <c r="B286">
@@ -16034,7 +16008,7 @@
       </c>
     </row>
     <row r="287" spans="1:4">
-      <c r="A287" s="1" t="s">
+      <c r="A287" t="s">
         <v>349</v>
       </c>
       <c r="B287">
